--- a/output7/【河洛文讀注音-閩拼調符】《寒窯賦》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調符】《寒窯賦》.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD7DF6A0-C943-4763-97BE-DABE14AEC0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92303063-0E49-4E6D-97E9-8180F3EBD16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
@@ -2650,10 +2650,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://i2.kknews.cc/QBPzr5vQGRFzOQ0l0v9KV7L-0ryvrh4tw48tEPA/0.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ciau1</t>
   </si>
   <si>
@@ -5675,6 +5671,10 @@
   </si>
   <si>
     <t>【河洛文讀注音-閩拼調符】《寒窯賦》.xlsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Han5-Iau7-Hu2.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7903,7 +7903,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -7919,7 +7919,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>802</v>
+        <v>1646</v>
       </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
@@ -7943,7 +7943,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="10" spans="2:11">
@@ -7979,7 +7979,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="30">
@@ -7987,7 +7987,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="48" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="30">
@@ -7995,7 +7995,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="30">
@@ -8003,7 +8003,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30">
@@ -8011,7 +8011,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="48" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30">
@@ -8019,7 +8019,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -8027,7 +8027,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="48" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30">
@@ -8060,9 +8060,6 @@
       <formula1>" ,十五音, 雅俗通,方音符號,台語音標, 白話字, 台羅拼音,閩拼調號, 閩拼調符"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{19645626-5184-4FAE-9DF9-C9CA2DB212E1}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8074,16 +8071,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B1" t="s">
         <v>1642</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1643</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1644</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1645</v>
       </c>
     </row>
   </sheetData>
@@ -8099,16 +8096,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B1" t="s">
         <v>1642</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1643</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1644</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8122,7 +8119,7 @@
         <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8136,7 +8133,7 @@
         <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8150,7 +8147,7 @@
         <v>199</v>
       </c>
       <c r="D4" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8164,7 +8161,7 @@
         <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8178,7 +8175,7 @@
         <v>199</v>
       </c>
       <c r="D6" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8192,7 +8189,7 @@
         <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8206,7 +8203,7 @@
         <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8220,7 +8217,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8234,7 +8231,7 @@
         <v>199</v>
       </c>
       <c r="D10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8248,7 +8245,7 @@
         <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8256,13 +8253,13 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C12" t="s">
         <v>199</v>
       </c>
       <c r="D12" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8276,7 +8273,7 @@
         <v>199</v>
       </c>
       <c r="D13" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8290,7 +8287,7 @@
         <v>199</v>
       </c>
       <c r="D14" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8304,7 +8301,7 @@
         <v>199</v>
       </c>
       <c r="D15" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8318,7 +8315,7 @@
         <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -8332,7 +8329,7 @@
         <v>199</v>
       </c>
       <c r="D17" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -8346,7 +8343,7 @@
         <v>199</v>
       </c>
       <c r="D18" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -8360,7 +8357,7 @@
         <v>199</v>
       </c>
       <c r="D19" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -8374,7 +8371,7 @@
         <v>199</v>
       </c>
       <c r="D20" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -8388,7 +8385,7 @@
         <v>199</v>
       </c>
       <c r="D21" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -8402,7 +8399,7 @@
         <v>199</v>
       </c>
       <c r="D22" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -8416,7 +8413,7 @@
         <v>199</v>
       </c>
       <c r="D23" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -8430,7 +8427,7 @@
         <v>199</v>
       </c>
       <c r="D24" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -8444,7 +8441,7 @@
         <v>199</v>
       </c>
       <c r="D25" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -8458,7 +8455,7 @@
         <v>199</v>
       </c>
       <c r="D26" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -8466,13 +8463,13 @@
         <v>673</v>
       </c>
       <c r="B27" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C27" t="s">
         <v>199</v>
       </c>
       <c r="D27" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -8486,7 +8483,7 @@
         <v>199</v>
       </c>
       <c r="D28" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -8500,7 +8497,7 @@
         <v>199</v>
       </c>
       <c r="D29" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -8514,7 +8511,7 @@
         <v>199</v>
       </c>
       <c r="D30" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -8528,7 +8525,7 @@
         <v>199</v>
       </c>
       <c r="D31" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -8542,7 +8539,7 @@
         <v>199</v>
       </c>
       <c r="D32" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -8556,7 +8553,7 @@
         <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -8570,7 +8567,7 @@
         <v>199</v>
       </c>
       <c r="D34" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -8584,7 +8581,7 @@
         <v>199</v>
       </c>
       <c r="D35" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -8592,13 +8589,13 @@
         <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C36" t="s">
         <v>199</v>
       </c>
       <c r="D36" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -8612,7 +8609,7 @@
         <v>199</v>
       </c>
       <c r="D37" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -8626,7 +8623,7 @@
         <v>199</v>
       </c>
       <c r="D38" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -8640,7 +8637,7 @@
         <v>199</v>
       </c>
       <c r="D39" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -8654,7 +8651,7 @@
         <v>199</v>
       </c>
       <c r="D40" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -8668,7 +8665,7 @@
         <v>199</v>
       </c>
       <c r="D41" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -8682,7 +8679,7 @@
         <v>199</v>
       </c>
       <c r="D42" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -8696,7 +8693,7 @@
         <v>199</v>
       </c>
       <c r="D43" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -8710,7 +8707,7 @@
         <v>199</v>
       </c>
       <c r="D44" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -8724,7 +8721,7 @@
         <v>199</v>
       </c>
       <c r="D45" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -8738,7 +8735,7 @@
         <v>199</v>
       </c>
       <c r="D46" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -8752,7 +8749,7 @@
         <v>199</v>
       </c>
       <c r="D47" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -8766,7 +8763,7 @@
         <v>199</v>
       </c>
       <c r="D48" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -8774,13 +8771,13 @@
         <v>65</v>
       </c>
       <c r="B49" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C49" t="s">
         <v>199</v>
       </c>
       <c r="D49" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -8794,7 +8791,7 @@
         <v>199</v>
       </c>
       <c r="D50" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -8802,13 +8799,13 @@
         <v>617</v>
       </c>
       <c r="B51" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C51" t="s">
         <v>199</v>
       </c>
       <c r="D51" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -8822,7 +8819,7 @@
         <v>199</v>
       </c>
       <c r="D52" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -8836,7 +8833,7 @@
         <v>199</v>
       </c>
       <c r="D53" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -8850,7 +8847,7 @@
         <v>199</v>
       </c>
       <c r="D54" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -8864,7 +8861,7 @@
         <v>199</v>
       </c>
       <c r="D55" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -8878,7 +8875,7 @@
         <v>199</v>
       </c>
       <c r="D56" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -8892,7 +8889,7 @@
         <v>199</v>
       </c>
       <c r="D57" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -8906,7 +8903,7 @@
         <v>199</v>
       </c>
       <c r="D58" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -8920,7 +8917,7 @@
         <v>199</v>
       </c>
       <c r="D59" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -8934,7 +8931,7 @@
         <v>199</v>
       </c>
       <c r="D60" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -8948,7 +8945,7 @@
         <v>199</v>
       </c>
       <c r="D61" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -8962,7 +8959,7 @@
         <v>199</v>
       </c>
       <c r="D62" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -8976,7 +8973,7 @@
         <v>199</v>
       </c>
       <c r="D63" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -8990,7 +8987,7 @@
         <v>199</v>
       </c>
       <c r="D64" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -8998,13 +8995,13 @@
         <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="C65" t="s">
         <v>199</v>
       </c>
       <c r="D65" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -9018,7 +9015,7 @@
         <v>199</v>
       </c>
       <c r="D66" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -9032,7 +9029,7 @@
         <v>199</v>
       </c>
       <c r="D67" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -9046,7 +9043,7 @@
         <v>199</v>
       </c>
       <c r="D68" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -9060,7 +9057,7 @@
         <v>199</v>
       </c>
       <c r="D69" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -9068,13 +9065,13 @@
         <v>414</v>
       </c>
       <c r="B70" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C70" t="s">
         <v>199</v>
       </c>
       <c r="D70" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -9088,7 +9085,7 @@
         <v>199</v>
       </c>
       <c r="D71" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -9102,7 +9099,7 @@
         <v>199</v>
       </c>
       <c r="D72" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -9116,7 +9113,7 @@
         <v>199</v>
       </c>
       <c r="D73" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -9130,7 +9127,7 @@
         <v>199</v>
       </c>
       <c r="D74" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -9144,7 +9141,7 @@
         <v>199</v>
       </c>
       <c r="D75" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -9158,7 +9155,7 @@
         <v>199</v>
       </c>
       <c r="D76" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -9172,7 +9169,7 @@
         <v>199</v>
       </c>
       <c r="D77" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -9186,7 +9183,7 @@
         <v>199</v>
       </c>
       <c r="D78" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -9194,13 +9191,13 @@
         <v>384</v>
       </c>
       <c r="B79" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C79" t="s">
         <v>199</v>
       </c>
       <c r="D79" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -9214,7 +9211,7 @@
         <v>199</v>
       </c>
       <c r="D80" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -9222,13 +9219,13 @@
         <v>629</v>
       </c>
       <c r="B81" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C81" t="s">
         <v>199</v>
       </c>
       <c r="D81" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -9242,7 +9239,7 @@
         <v>199</v>
       </c>
       <c r="D82" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -9270,7 +9267,7 @@
         <v>199</v>
       </c>
       <c r="D84" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -9284,7 +9281,7 @@
         <v>199</v>
       </c>
       <c r="D85" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -9298,7 +9295,7 @@
         <v>199</v>
       </c>
       <c r="D86" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -9326,7 +9323,7 @@
         <v>199</v>
       </c>
       <c r="D88" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -9340,7 +9337,7 @@
         <v>199</v>
       </c>
       <c r="D89" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -9354,7 +9351,7 @@
         <v>199</v>
       </c>
       <c r="D90" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -9368,7 +9365,7 @@
         <v>199</v>
       </c>
       <c r="D91" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -9382,7 +9379,7 @@
         <v>199</v>
       </c>
       <c r="D92" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -9396,7 +9393,7 @@
         <v>199</v>
       </c>
       <c r="D93" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -9410,7 +9407,7 @@
         <v>199</v>
       </c>
       <c r="D94" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -9424,7 +9421,7 @@
         <v>199</v>
       </c>
       <c r="D95" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -9438,7 +9435,7 @@
         <v>199</v>
       </c>
       <c r="D96" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -9446,13 +9443,13 @@
         <v>31</v>
       </c>
       <c r="B97" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C97" t="s">
         <v>199</v>
       </c>
       <c r="D97" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -9466,7 +9463,7 @@
         <v>199</v>
       </c>
       <c r="D98" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -9480,7 +9477,7 @@
         <v>199</v>
       </c>
       <c r="D99" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -9494,7 +9491,7 @@
         <v>199</v>
       </c>
       <c r="D100" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -9508,7 +9505,7 @@
         <v>199</v>
       </c>
       <c r="D101" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -9522,7 +9519,7 @@
         <v>199</v>
       </c>
       <c r="D102" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -9536,7 +9533,7 @@
         <v>199</v>
       </c>
       <c r="D103" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -9550,7 +9547,7 @@
         <v>199</v>
       </c>
       <c r="D104" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -9564,7 +9561,7 @@
         <v>199</v>
       </c>
       <c r="D105" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -9578,7 +9575,7 @@
         <v>199</v>
       </c>
       <c r="D106" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -9592,7 +9589,7 @@
         <v>199</v>
       </c>
       <c r="D107" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -9606,7 +9603,7 @@
         <v>199</v>
       </c>
       <c r="D108" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -9620,7 +9617,7 @@
         <v>199</v>
       </c>
       <c r="D109" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -9634,7 +9631,7 @@
         <v>199</v>
       </c>
       <c r="D110" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -9648,7 +9645,7 @@
         <v>199</v>
       </c>
       <c r="D111" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -9662,7 +9659,7 @@
         <v>199</v>
       </c>
       <c r="D112" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -9670,13 +9667,13 @@
         <v>94</v>
       </c>
       <c r="B113" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="C113" t="s">
         <v>199</v>
       </c>
       <c r="D113" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -9690,12 +9687,12 @@
         <v>199</v>
       </c>
       <c r="D114" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B115" t="s">
         <v>129</v>
@@ -9704,7 +9701,7 @@
         <v>199</v>
       </c>
       <c r="D115" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -9718,7 +9715,7 @@
         <v>199</v>
       </c>
       <c r="D116" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -9732,7 +9729,7 @@
         <v>199</v>
       </c>
       <c r="D117" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -9746,7 +9743,7 @@
         <v>199</v>
       </c>
       <c r="D118" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -9760,7 +9757,7 @@
         <v>199</v>
       </c>
       <c r="D119" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -9774,7 +9771,7 @@
         <v>199</v>
       </c>
       <c r="D120" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -9788,7 +9785,7 @@
         <v>199</v>
       </c>
       <c r="D121" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -9802,7 +9799,7 @@
         <v>199</v>
       </c>
       <c r="D122" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -9816,7 +9813,7 @@
         <v>199</v>
       </c>
       <c r="D123" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -9830,7 +9827,7 @@
         <v>199</v>
       </c>
       <c r="D124" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -9844,7 +9841,7 @@
         <v>199</v>
       </c>
       <c r="D125" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -9858,7 +9855,7 @@
         <v>199</v>
       </c>
       <c r="D126" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -9872,7 +9869,7 @@
         <v>199</v>
       </c>
       <c r="D127" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -9886,7 +9883,7 @@
         <v>199</v>
       </c>
       <c r="D128" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -9900,7 +9897,7 @@
         <v>199</v>
       </c>
       <c r="D129" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -9914,7 +9911,7 @@
         <v>199</v>
       </c>
       <c r="D130" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -9922,13 +9919,13 @@
         <v>108</v>
       </c>
       <c r="B131" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="C131" t="s">
         <v>199</v>
       </c>
       <c r="D131" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -9942,7 +9939,7 @@
         <v>199</v>
       </c>
       <c r="D132" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -9956,7 +9953,7 @@
         <v>199</v>
       </c>
       <c r="D133" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -9970,7 +9967,7 @@
         <v>199</v>
       </c>
       <c r="D134" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -9984,7 +9981,7 @@
         <v>199</v>
       </c>
       <c r="D135" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -9998,7 +9995,7 @@
         <v>199</v>
       </c>
       <c r="D136" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -10012,7 +10009,7 @@
         <v>199</v>
       </c>
       <c r="D137" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -10026,7 +10023,7 @@
         <v>199</v>
       </c>
       <c r="D138" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -10040,7 +10037,7 @@
         <v>199</v>
       </c>
       <c r="D139" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -10054,7 +10051,7 @@
         <v>199</v>
       </c>
       <c r="D140" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -10068,7 +10065,7 @@
         <v>199</v>
       </c>
       <c r="D141" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -10082,7 +10079,7 @@
         <v>199</v>
       </c>
       <c r="D142" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -10096,7 +10093,7 @@
         <v>199</v>
       </c>
       <c r="D143" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -10110,7 +10107,7 @@
         <v>199</v>
       </c>
       <c r="D144" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -10124,7 +10121,7 @@
         <v>199</v>
       </c>
       <c r="D145" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -10138,7 +10135,7 @@
         <v>199</v>
       </c>
       <c r="D146" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -10152,7 +10149,7 @@
         <v>199</v>
       </c>
       <c r="D147" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -10166,7 +10163,7 @@
         <v>199</v>
       </c>
       <c r="D148" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -10180,7 +10177,7 @@
         <v>199</v>
       </c>
       <c r="D149" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -10194,7 +10191,7 @@
         <v>199</v>
       </c>
       <c r="D150" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -10208,7 +10205,7 @@
         <v>199</v>
       </c>
       <c r="D151" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -10222,7 +10219,7 @@
         <v>199</v>
       </c>
       <c r="D152" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -10236,7 +10233,7 @@
         <v>199</v>
       </c>
       <c r="D153" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -10250,7 +10247,7 @@
         <v>199</v>
       </c>
       <c r="D154" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -10264,7 +10261,7 @@
         <v>199</v>
       </c>
       <c r="D155" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -10278,7 +10275,7 @@
         <v>199</v>
       </c>
       <c r="D156" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -10292,7 +10289,7 @@
         <v>199</v>
       </c>
       <c r="D157" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -10306,7 +10303,7 @@
         <v>199</v>
       </c>
       <c r="D158" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -10320,7 +10317,7 @@
         <v>199</v>
       </c>
       <c r="D159" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -10334,7 +10331,7 @@
         <v>199</v>
       </c>
       <c r="D160" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -10348,7 +10345,7 @@
         <v>199</v>
       </c>
       <c r="D161" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -10362,7 +10359,7 @@
         <v>199</v>
       </c>
       <c r="D162" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -10376,7 +10373,7 @@
         <v>199</v>
       </c>
       <c r="D163" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -10390,7 +10387,7 @@
         <v>199</v>
       </c>
       <c r="D164" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -10398,13 +10395,13 @@
         <v>488</v>
       </c>
       <c r="B165" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C165" t="s">
         <v>199</v>
       </c>
       <c r="D165" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -10418,7 +10415,7 @@
         <v>199</v>
       </c>
       <c r="D166" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -10432,7 +10429,7 @@
         <v>199</v>
       </c>
       <c r="D167" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -10446,7 +10443,7 @@
         <v>199</v>
       </c>
       <c r="D168" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -10460,7 +10457,7 @@
         <v>199</v>
       </c>
       <c r="D169" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -10474,7 +10471,7 @@
         <v>199</v>
       </c>
       <c r="D170" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -10488,7 +10485,7 @@
         <v>199</v>
       </c>
       <c r="D171" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -10502,7 +10499,7 @@
         <v>199</v>
       </c>
       <c r="D172" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -10516,7 +10513,7 @@
         <v>199</v>
       </c>
       <c r="D173" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -10530,7 +10527,7 @@
         <v>199</v>
       </c>
       <c r="D174" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -10544,7 +10541,7 @@
         <v>199</v>
       </c>
       <c r="D175" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -10558,7 +10555,7 @@
         <v>199</v>
       </c>
       <c r="D176" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -10572,7 +10569,7 @@
         <v>199</v>
       </c>
       <c r="D177" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -10586,7 +10583,7 @@
         <v>199</v>
       </c>
       <c r="D178" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -10600,7 +10597,7 @@
         <v>199</v>
       </c>
       <c r="D179" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -10614,7 +10611,7 @@
         <v>199</v>
       </c>
       <c r="D180" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -10628,7 +10625,7 @@
         <v>199</v>
       </c>
       <c r="D181" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -10642,7 +10639,7 @@
         <v>199</v>
       </c>
       <c r="D182" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -10656,7 +10653,7 @@
         <v>199</v>
       </c>
       <c r="D183" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -10670,7 +10667,7 @@
         <v>199</v>
       </c>
       <c r="D184" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -10684,7 +10681,7 @@
         <v>199</v>
       </c>
       <c r="D185" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -10698,7 +10695,7 @@
         <v>199</v>
       </c>
       <c r="D186" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -10712,7 +10709,7 @@
         <v>199</v>
       </c>
       <c r="D187" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -10726,7 +10723,7 @@
         <v>199</v>
       </c>
       <c r="D188" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -10740,7 +10737,7 @@
         <v>199</v>
       </c>
       <c r="D189" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -10754,7 +10751,7 @@
         <v>199</v>
       </c>
       <c r="D190" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -10768,7 +10765,7 @@
         <v>199</v>
       </c>
       <c r="D191" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -10782,7 +10779,7 @@
         <v>199</v>
       </c>
       <c r="D192" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -10796,7 +10793,7 @@
         <v>199</v>
       </c>
       <c r="D193" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -10810,7 +10807,7 @@
         <v>199</v>
       </c>
       <c r="D194" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -10824,7 +10821,7 @@
         <v>199</v>
       </c>
       <c r="D195" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -10838,7 +10835,7 @@
         <v>199</v>
       </c>
       <c r="D196" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -10852,7 +10849,7 @@
         <v>199</v>
       </c>
       <c r="D197" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -10866,7 +10863,7 @@
         <v>199</v>
       </c>
       <c r="D198" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -10880,7 +10877,7 @@
         <v>199</v>
       </c>
       <c r="D199" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -10888,13 +10885,13 @@
         <v>614</v>
       </c>
       <c r="B200" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C200" t="s">
         <v>199</v>
       </c>
       <c r="D200" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -10908,7 +10905,7 @@
         <v>199</v>
       </c>
       <c r="D201" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -10922,7 +10919,7 @@
         <v>199</v>
       </c>
       <c r="D202" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -10936,7 +10933,7 @@
         <v>199</v>
       </c>
       <c r="D203" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -10950,7 +10947,7 @@
         <v>199</v>
       </c>
       <c r="D204" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -10964,7 +10961,7 @@
         <v>199</v>
       </c>
       <c r="D205" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -10978,7 +10975,7 @@
         <v>199</v>
       </c>
       <c r="D206" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -10992,7 +10989,7 @@
         <v>199</v>
       </c>
       <c r="D207" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -11006,7 +11003,7 @@
         <v>199</v>
       </c>
       <c r="D208" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -11020,7 +11017,7 @@
         <v>199</v>
       </c>
       <c r="D209" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -11034,7 +11031,7 @@
         <v>199</v>
       </c>
       <c r="D210" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -11048,7 +11045,7 @@
         <v>199</v>
       </c>
       <c r="D211" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -11062,7 +11059,7 @@
         <v>199</v>
       </c>
       <c r="D212" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -11076,7 +11073,7 @@
         <v>199</v>
       </c>
       <c r="D213" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -11090,7 +11087,7 @@
         <v>199</v>
       </c>
       <c r="D214" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -11104,7 +11101,7 @@
         <v>199</v>
       </c>
       <c r="D215" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -11118,7 +11115,7 @@
         <v>199</v>
       </c>
       <c r="D216" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -11132,7 +11129,7 @@
         <v>199</v>
       </c>
       <c r="D217" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -11146,7 +11143,7 @@
         <v>199</v>
       </c>
       <c r="D218" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -11160,7 +11157,7 @@
         <v>199</v>
       </c>
       <c r="D219" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -11174,7 +11171,7 @@
         <v>199</v>
       </c>
       <c r="D220" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -11188,7 +11185,7 @@
         <v>199</v>
       </c>
       <c r="D221" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -11202,7 +11199,7 @@
         <v>199</v>
       </c>
       <c r="D222" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -11216,7 +11213,7 @@
         <v>199</v>
       </c>
       <c r="D223" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -11230,7 +11227,7 @@
         <v>199</v>
       </c>
       <c r="D224" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -11244,7 +11241,7 @@
         <v>199</v>
       </c>
       <c r="D225" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -11258,7 +11255,7 @@
         <v>199</v>
       </c>
       <c r="D226" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -11272,7 +11269,7 @@
         <v>199</v>
       </c>
       <c r="D227" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -11286,7 +11283,7 @@
         <v>199</v>
       </c>
       <c r="D228" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -11300,7 +11297,7 @@
         <v>199</v>
       </c>
       <c r="D229" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -11314,7 +11311,7 @@
         <v>199</v>
       </c>
       <c r="D230" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -11328,7 +11325,7 @@
         <v>199</v>
       </c>
       <c r="D231" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -11342,7 +11339,7 @@
         <v>199</v>
       </c>
       <c r="D232" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -11356,7 +11353,7 @@
         <v>199</v>
       </c>
       <c r="D233" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -11370,7 +11367,7 @@
         <v>199</v>
       </c>
       <c r="D234" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -11384,7 +11381,7 @@
         <v>199</v>
       </c>
       <c r="D235" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -11392,13 +11389,13 @@
         <v>481</v>
       </c>
       <c r="B236" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="C236" t="s">
         <v>199</v>
       </c>
       <c r="D236" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -11412,7 +11409,7 @@
         <v>199</v>
       </c>
       <c r="D237" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -11426,7 +11423,7 @@
         <v>199</v>
       </c>
       <c r="D238" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -11440,7 +11437,7 @@
         <v>199</v>
       </c>
       <c r="D239" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -11454,7 +11451,7 @@
         <v>199</v>
       </c>
       <c r="D240" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -11468,7 +11465,7 @@
         <v>199</v>
       </c>
       <c r="D241" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -11482,7 +11479,7 @@
         <v>199</v>
       </c>
       <c r="D242" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -11496,7 +11493,7 @@
         <v>199</v>
       </c>
       <c r="D243" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -11510,7 +11507,7 @@
         <v>199</v>
       </c>
       <c r="D244" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -11524,7 +11521,7 @@
         <v>199</v>
       </c>
       <c r="D245" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -11538,7 +11535,7 @@
         <v>199</v>
       </c>
       <c r="D246" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -11552,7 +11549,7 @@
         <v>199</v>
       </c>
       <c r="D247" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -11566,7 +11563,7 @@
         <v>199</v>
       </c>
       <c r="D248" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -11580,7 +11577,7 @@
         <v>199</v>
       </c>
       <c r="D249" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -11594,7 +11591,7 @@
         <v>199</v>
       </c>
       <c r="D250" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -11608,7 +11605,7 @@
         <v>199</v>
       </c>
       <c r="D251" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -11622,7 +11619,7 @@
         <v>199</v>
       </c>
       <c r="D252" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -11636,7 +11633,7 @@
         <v>199</v>
       </c>
       <c r="D253" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -11650,7 +11647,7 @@
         <v>199</v>
       </c>
       <c r="D254" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -11664,7 +11661,7 @@
         <v>199</v>
       </c>
       <c r="D255" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -11678,7 +11675,7 @@
         <v>199</v>
       </c>
       <c r="D256" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -11692,7 +11689,7 @@
         <v>199</v>
       </c>
       <c r="D257" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -11706,7 +11703,7 @@
         <v>199</v>
       </c>
       <c r="D258" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -11720,7 +11717,7 @@
         <v>199</v>
       </c>
       <c r="D259" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -11734,7 +11731,7 @@
         <v>199</v>
       </c>
       <c r="D260" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -11748,7 +11745,7 @@
         <v>199</v>
       </c>
       <c r="D261" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -11756,13 +11753,13 @@
         <v>575</v>
       </c>
       <c r="B262" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C262" t="s">
         <v>199</v>
       </c>
       <c r="D262" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -11776,7 +11773,7 @@
         <v>199</v>
       </c>
       <c r="D263" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -11790,7 +11787,7 @@
         <v>199</v>
       </c>
       <c r="D264" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -11804,7 +11801,7 @@
         <v>199</v>
       </c>
       <c r="D265" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -11818,7 +11815,7 @@
         <v>199</v>
       </c>
       <c r="D266" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -11832,7 +11829,7 @@
         <v>199</v>
       </c>
       <c r="D267" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -11846,7 +11843,7 @@
         <v>199</v>
       </c>
       <c r="D268" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -11860,7 +11857,7 @@
         <v>199</v>
       </c>
       <c r="D269" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -11874,7 +11871,7 @@
         <v>199</v>
       </c>
       <c r="D270" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -11888,7 +11885,7 @@
         <v>199</v>
       </c>
       <c r="D271" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -11902,7 +11899,7 @@
         <v>199</v>
       </c>
       <c r="D272" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -11916,7 +11913,7 @@
         <v>199</v>
       </c>
       <c r="D273" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -11930,7 +11927,7 @@
         <v>199</v>
       </c>
       <c r="D274" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -11944,7 +11941,7 @@
         <v>199</v>
       </c>
       <c r="D275" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -11958,7 +11955,7 @@
         <v>199</v>
       </c>
       <c r="D276" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -11972,7 +11969,7 @@
         <v>199</v>
       </c>
       <c r="D277" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -11986,7 +11983,7 @@
         <v>199</v>
       </c>
       <c r="D278" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -12000,7 +11997,7 @@
         <v>199</v>
       </c>
       <c r="D279" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -12014,7 +12011,7 @@
         <v>199</v>
       </c>
       <c r="D280" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -12028,7 +12025,7 @@
         <v>199</v>
       </c>
       <c r="D281" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -12042,7 +12039,7 @@
         <v>199</v>
       </c>
       <c r="D282" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -12056,7 +12053,7 @@
         <v>199</v>
       </c>
       <c r="D283" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -12070,7 +12067,7 @@
         <v>199</v>
       </c>
       <c r="D284" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -12084,7 +12081,7 @@
         <v>199</v>
       </c>
       <c r="D285" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -12092,13 +12089,13 @@
         <v>18</v>
       </c>
       <c r="B286" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="C286" t="s">
         <v>199</v>
       </c>
       <c r="D286" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -12112,7 +12109,7 @@
         <v>199</v>
       </c>
       <c r="D287" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -12126,7 +12123,7 @@
         <v>199</v>
       </c>
       <c r="D288" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -12140,7 +12137,7 @@
         <v>199</v>
       </c>
       <c r="D289" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -12154,7 +12151,7 @@
         <v>199</v>
       </c>
       <c r="D290" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -12168,7 +12165,7 @@
         <v>199</v>
       </c>
       <c r="D291" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -12176,13 +12173,13 @@
         <v>75</v>
       </c>
       <c r="B292" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="C292" t="s">
         <v>199</v>
       </c>
       <c r="D292" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -12196,7 +12193,7 @@
         <v>199</v>
       </c>
       <c r="D293" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -12210,7 +12207,7 @@
         <v>199</v>
       </c>
       <c r="D294" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -12224,7 +12221,7 @@
         <v>199</v>
       </c>
       <c r="D295" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -12238,7 +12235,7 @@
         <v>199</v>
       </c>
       <c r="D296" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -12252,7 +12249,7 @@
         <v>199</v>
       </c>
       <c r="D297" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -12266,7 +12263,7 @@
         <v>199</v>
       </c>
       <c r="D298" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -12280,7 +12277,7 @@
         <v>199</v>
       </c>
       <c r="D299" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -12294,7 +12291,7 @@
         <v>199</v>
       </c>
       <c r="D300" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -12308,7 +12305,7 @@
         <v>199</v>
       </c>
       <c r="D301" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -12322,7 +12319,7 @@
         <v>199</v>
       </c>
       <c r="D302" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -12336,7 +12333,7 @@
         <v>199</v>
       </c>
       <c r="D303" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -12350,7 +12347,7 @@
         <v>199</v>
       </c>
       <c r="D304" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -12364,7 +12361,7 @@
         <v>199</v>
       </c>
       <c r="D305" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -12378,7 +12375,7 @@
         <v>199</v>
       </c>
       <c r="D306" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -12392,7 +12389,7 @@
         <v>199</v>
       </c>
       <c r="D307" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -12406,7 +12403,7 @@
         <v>199</v>
       </c>
       <c r="D308" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -12420,7 +12417,7 @@
         <v>199</v>
       </c>
       <c r="D309" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -12434,7 +12431,7 @@
         <v>199</v>
       </c>
       <c r="D310" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -12448,7 +12445,7 @@
         <v>199</v>
       </c>
       <c r="D311" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -12462,7 +12459,7 @@
         <v>199</v>
       </c>
       <c r="D312" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -12476,7 +12473,7 @@
         <v>199</v>
       </c>
       <c r="D313" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -12490,7 +12487,7 @@
         <v>199</v>
       </c>
       <c r="D314" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -12504,7 +12501,7 @@
         <v>199</v>
       </c>
       <c r="D315" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -12518,7 +12515,7 @@
         <v>199</v>
       </c>
       <c r="D316" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -12532,7 +12529,7 @@
         <v>199</v>
       </c>
       <c r="D317" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -12546,7 +12543,7 @@
         <v>199</v>
       </c>
       <c r="D318" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -12560,7 +12557,7 @@
         <v>199</v>
       </c>
       <c r="D319" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -12574,7 +12571,7 @@
         <v>199</v>
       </c>
       <c r="D320" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -12588,7 +12585,7 @@
         <v>199</v>
       </c>
       <c r="D321" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -12602,7 +12599,7 @@
         <v>199</v>
       </c>
       <c r="D322" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -12616,7 +12613,7 @@
         <v>199</v>
       </c>
       <c r="D323" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -12630,7 +12627,7 @@
         <v>199</v>
       </c>
       <c r="D324" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -12644,7 +12641,7 @@
         <v>199</v>
       </c>
       <c r="D325" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -12658,7 +12655,7 @@
         <v>199</v>
       </c>
       <c r="D326" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -12672,7 +12669,7 @@
         <v>199</v>
       </c>
       <c r="D327" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -12686,7 +12683,7 @@
         <v>199</v>
       </c>
       <c r="D328" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -12700,7 +12697,7 @@
         <v>199</v>
       </c>
       <c r="D329" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -12714,7 +12711,7 @@
         <v>199</v>
       </c>
       <c r="D330" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -12728,7 +12725,7 @@
         <v>199</v>
       </c>
       <c r="D331" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -12742,7 +12739,7 @@
         <v>199</v>
       </c>
       <c r="D332" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -12756,7 +12753,7 @@
         <v>199</v>
       </c>
       <c r="D333" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -12770,7 +12767,7 @@
         <v>199</v>
       </c>
       <c r="D334" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -12778,13 +12775,13 @@
         <v>438</v>
       </c>
       <c r="B335" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="C335" t="s">
         <v>199</v>
       </c>
       <c r="D335" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -12798,7 +12795,7 @@
         <v>199</v>
       </c>
       <c r="D336" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -12812,7 +12809,7 @@
         <v>199</v>
       </c>
       <c r="D337" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -12826,7 +12823,7 @@
         <v>199</v>
       </c>
       <c r="D338" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -12840,7 +12837,7 @@
         <v>199</v>
       </c>
       <c r="D339" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -12854,7 +12851,7 @@
         <v>199</v>
       </c>
       <c r="D340" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -12862,13 +12859,13 @@
         <v>524</v>
       </c>
       <c r="B341" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C341" t="s">
         <v>199</v>
       </c>
       <c r="D341" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -12882,7 +12879,7 @@
         <v>199</v>
       </c>
       <c r="D342" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
   </sheetData>
@@ -12898,16 +12895,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B1" t="s">
         <v>1642</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1643</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1644</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -12921,7 +12918,7 @@
         <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -12935,7 +12932,7 @@
         <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -12949,7 +12946,7 @@
         <v>199</v>
       </c>
       <c r="D4" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -12963,7 +12960,7 @@
         <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -12977,7 +12974,7 @@
         <v>199</v>
       </c>
       <c r="D6" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -12991,7 +12988,7 @@
         <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -13005,7 +13002,7 @@
         <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -13019,7 +13016,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -13033,7 +13030,7 @@
         <v>199</v>
       </c>
       <c r="D10" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -13047,7 +13044,7 @@
         <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -13061,7 +13058,7 @@
         <v>199</v>
       </c>
       <c r="D12" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -13075,7 +13072,7 @@
         <v>199</v>
       </c>
       <c r="D13" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -13089,7 +13086,7 @@
         <v>199</v>
       </c>
       <c r="D14" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -13103,7 +13100,7 @@
         <v>199</v>
       </c>
       <c r="D15" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -13117,7 +13114,7 @@
         <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -13131,7 +13128,7 @@
         <v>199</v>
       </c>
       <c r="D17" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -13145,7 +13142,7 @@
         <v>199</v>
       </c>
       <c r="D18" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -13159,7 +13156,7 @@
         <v>199</v>
       </c>
       <c r="D19" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -13173,7 +13170,7 @@
         <v>199</v>
       </c>
       <c r="D20" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -13187,7 +13184,7 @@
         <v>199</v>
       </c>
       <c r="D21" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -13201,7 +13198,7 @@
         <v>199</v>
       </c>
       <c r="D22" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -13209,13 +13206,13 @@
         <v>414</v>
       </c>
       <c r="B23" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C23" t="s">
         <v>199</v>
       </c>
       <c r="D23" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -13229,7 +13226,7 @@
         <v>199</v>
       </c>
       <c r="D24" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -13237,13 +13234,13 @@
         <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="C25" t="s">
         <v>199</v>
       </c>
       <c r="D25" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -13257,7 +13254,7 @@
         <v>199</v>
       </c>
       <c r="D26" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -13271,7 +13268,7 @@
         <v>199</v>
       </c>
       <c r="D27" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -13285,7 +13282,7 @@
         <v>199</v>
       </c>
       <c r="D28" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -13299,7 +13296,7 @@
         <v>199</v>
       </c>
       <c r="D29" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -13313,7 +13310,7 @@
         <v>199</v>
       </c>
       <c r="D30" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -13327,7 +13324,7 @@
         <v>199</v>
       </c>
       <c r="D31" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -13341,7 +13338,7 @@
         <v>199</v>
       </c>
       <c r="D32" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -13355,7 +13352,7 @@
         <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -13363,18 +13360,18 @@
         <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="C34" t="s">
         <v>199</v>
       </c>
       <c r="D34" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B35" t="s">
         <v>129</v>
@@ -13383,7 +13380,7 @@
         <v>199</v>
       </c>
       <c r="D35" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -13397,7 +13394,7 @@
         <v>199</v>
       </c>
       <c r="D36" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -13411,7 +13408,7 @@
         <v>199</v>
       </c>
       <c r="D37" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -13425,7 +13422,7 @@
         <v>199</v>
       </c>
       <c r="D38" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -13439,7 +13436,7 @@
         <v>199</v>
       </c>
       <c r="D39" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -13453,7 +13450,7 @@
         <v>199</v>
       </c>
       <c r="D40" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -13467,7 +13464,7 @@
         <v>199</v>
       </c>
       <c r="D41" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -13481,7 +13478,7 @@
         <v>199</v>
       </c>
       <c r="D42" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -13495,7 +13492,7 @@
         <v>199</v>
       </c>
       <c r="D43" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -13509,7 +13506,7 @@
         <v>199</v>
       </c>
       <c r="D44" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -13523,7 +13520,7 @@
         <v>199</v>
       </c>
       <c r="D45" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -13537,7 +13534,7 @@
         <v>199</v>
       </c>
       <c r="D46" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -13551,7 +13548,7 @@
         <v>199</v>
       </c>
       <c r="D47" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -13565,7 +13562,7 @@
         <v>199</v>
       </c>
       <c r="D48" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -13579,7 +13576,7 @@
         <v>199</v>
       </c>
       <c r="D49" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -13593,7 +13590,7 @@
         <v>199</v>
       </c>
       <c r="D50" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -13607,7 +13604,7 @@
         <v>199</v>
       </c>
       <c r="D51" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -13621,7 +13618,7 @@
         <v>199</v>
       </c>
       <c r="D52" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -13635,7 +13632,7 @@
         <v>199</v>
       </c>
       <c r="D53" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -13649,7 +13646,7 @@
         <v>199</v>
       </c>
       <c r="D54" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -13663,7 +13660,7 @@
         <v>199</v>
       </c>
       <c r="D55" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -13677,7 +13674,7 @@
         <v>199</v>
       </c>
       <c r="D56" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -13691,7 +13688,7 @@
         <v>199</v>
       </c>
       <c r="D57" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -13705,7 +13702,7 @@
         <v>199</v>
       </c>
       <c r="D58" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -13719,7 +13716,7 @@
         <v>199</v>
       </c>
       <c r="D59" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -13733,7 +13730,7 @@
         <v>199</v>
       </c>
       <c r="D60" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -13747,7 +13744,7 @@
         <v>199</v>
       </c>
       <c r="D61" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -13761,7 +13758,7 @@
         <v>199</v>
       </c>
       <c r="D62" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -13775,7 +13772,7 @@
         <v>199</v>
       </c>
       <c r="D63" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -13789,7 +13786,7 @@
         <v>199</v>
       </c>
       <c r="D64" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -13803,7 +13800,7 @@
         <v>199</v>
       </c>
       <c r="D65" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -13817,7 +13814,7 @@
         <v>199</v>
       </c>
       <c r="D66" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -13831,7 +13828,7 @@
         <v>199</v>
       </c>
       <c r="D67" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -13845,7 +13842,7 @@
         <v>199</v>
       </c>
       <c r="D68" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -13859,7 +13856,7 @@
         <v>199</v>
       </c>
       <c r="D69" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -13873,7 +13870,7 @@
         <v>199</v>
       </c>
       <c r="D70" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -13887,7 +13884,7 @@
         <v>199</v>
       </c>
       <c r="D71" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -13901,7 +13898,7 @@
         <v>199</v>
       </c>
       <c r="D72" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -13909,13 +13906,13 @@
         <v>481</v>
       </c>
       <c r="B73" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="C73" t="s">
         <v>199</v>
       </c>
       <c r="D73" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -13929,7 +13926,7 @@
         <v>199</v>
       </c>
       <c r="D74" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -13943,7 +13940,7 @@
         <v>199</v>
       </c>
       <c r="D75" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -13957,7 +13954,7 @@
         <v>199</v>
       </c>
       <c r="D76" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -13971,7 +13968,7 @@
         <v>199</v>
       </c>
       <c r="D77" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -13985,7 +13982,7 @@
         <v>199</v>
       </c>
       <c r="D78" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -13999,7 +13996,7 @@
         <v>199</v>
       </c>
       <c r="D79" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -14013,7 +14010,7 @@
         <v>199</v>
       </c>
       <c r="D80" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -14027,7 +14024,7 @@
         <v>199</v>
       </c>
       <c r="D81" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -14041,7 +14038,7 @@
         <v>199</v>
       </c>
       <c r="D82" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -14055,7 +14052,7 @@
         <v>199</v>
       </c>
       <c r="D83" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -14069,7 +14066,7 @@
         <v>199</v>
       </c>
       <c r="D84" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -14083,7 +14080,7 @@
         <v>199</v>
       </c>
       <c r="D85" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -14091,13 +14088,13 @@
         <v>108</v>
       </c>
       <c r="B86" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="C86" t="s">
         <v>199</v>
       </c>
       <c r="D86" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -14111,7 +14108,7 @@
         <v>199</v>
       </c>
       <c r="D87" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -14125,7 +14122,7 @@
         <v>199</v>
       </c>
       <c r="D88" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -14139,7 +14136,7 @@
         <v>199</v>
       </c>
       <c r="D89" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -14153,7 +14150,7 @@
         <v>199</v>
       </c>
       <c r="D90" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -14167,7 +14164,7 @@
         <v>199</v>
       </c>
       <c r="D91" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -14181,7 +14178,7 @@
         <v>199</v>
       </c>
       <c r="D92" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -14195,7 +14192,7 @@
         <v>199</v>
       </c>
       <c r="D93" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -14209,7 +14206,7 @@
         <v>199</v>
       </c>
       <c r="D94" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -14217,13 +14214,13 @@
         <v>75</v>
       </c>
       <c r="B95" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="C95" t="s">
         <v>199</v>
       </c>
       <c r="D95" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -14231,13 +14228,13 @@
         <v>18</v>
       </c>
       <c r="B96" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="C96" t="s">
         <v>199</v>
       </c>
       <c r="D96" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -14251,7 +14248,7 @@
         <v>199</v>
       </c>
       <c r="D97" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -14265,7 +14262,7 @@
         <v>199</v>
       </c>
       <c r="D98" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -14279,7 +14276,7 @@
         <v>199</v>
       </c>
       <c r="D99" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -14293,7 +14290,7 @@
         <v>199</v>
       </c>
       <c r="D100" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -14301,13 +14298,13 @@
         <v>438</v>
       </c>
       <c r="B101" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="C101" t="s">
         <v>199</v>
       </c>
       <c r="D101" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -14315,13 +14312,13 @@
         <v>524</v>
       </c>
       <c r="B102" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C102" t="s">
         <v>199</v>
       </c>
       <c r="D102" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
   </sheetData>
@@ -14482,7 +14479,7 @@
       <c r="R3" s="54"/>
       <c r="T3" s="16"/>
       <c r="V3" s="61" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
@@ -14552,13 +14549,13 @@
       <c r="C6" s="23"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24" t="s">
+        <v>962</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>963</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="G6" s="24" t="s">
         <v>964</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>965</v>
       </c>
       <c r="H6" s="24"/>
       <c r="I6" s="24"/>
@@ -14791,45 +14788,45 @@
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
       <c r="D14" s="24" t="s">
+        <v>965</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>966</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="F14" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G14" s="24" t="s">
         <v>967</v>
       </c>
-      <c r="F14" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="G14" s="24" t="s">
+      <c r="H14" s="24" t="s">
         <v>968</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="I14" s="24" t="s">
         <v>969</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>970</v>
       </c>
       <c r="J14" s="24"/>
       <c r="K14" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="L14" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="M14" s="24" t="s">
+        <v>971</v>
+      </c>
+      <c r="N14" s="24" t="s">
         <v>972</v>
       </c>
-      <c r="N14" s="24" t="s">
+      <c r="O14" s="24" t="s">
         <v>973</v>
       </c>
-      <c r="O14" s="24" t="s">
+      <c r="P14" s="24" t="s">
         <v>974</v>
-      </c>
-      <c r="P14" s="24" t="s">
-        <v>975</v>
       </c>
       <c r="Q14" s="24"/>
       <c r="R14" s="24" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="S14" s="31"/>
       <c r="V14" s="62"/>
@@ -14849,7 +14846,7 @@
         <v>227</v>
       </c>
       <c r="I15" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J15" s="54"/>
       <c r="K15" s="54" t="s">
@@ -14901,7 +14898,7 @@
         <v>748</v>
       </c>
       <c r="P16" s="56" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="Q16" s="56"/>
       <c r="R16" s="56" t="s">
@@ -14966,43 +14963,43 @@
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
       <c r="D18" s="24" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E18" s="24" t="s">
         <v>1584</v>
       </c>
-      <c r="E18" s="24" t="s">
-        <v>1585</v>
-      </c>
       <c r="F18" s="24" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G18" s="24"/>
       <c r="H18" s="24" t="s">
+        <v>976</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="J18" s="24" t="s">
         <v>977</v>
       </c>
-      <c r="I18" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="J18" s="24" t="s">
+      <c r="K18" s="24" t="s">
         <v>978</v>
-      </c>
-      <c r="K18" s="24" t="s">
-        <v>979</v>
       </c>
       <c r="L18" s="24"/>
       <c r="M18" s="24" t="s">
+        <v>979</v>
+      </c>
+      <c r="N18" s="24" t="s">
         <v>980</v>
       </c>
-      <c r="N18" s="24" t="s">
+      <c r="O18" s="24" t="s">
         <v>981</v>
       </c>
-      <c r="O18" s="24" t="s">
-        <v>982</v>
-      </c>
       <c r="P18" s="24" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="Q18" s="24"/>
       <c r="R18" s="24" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="S18" s="31"/>
       <c r="V18" s="62"/>
@@ -15011,7 +15008,7 @@
       <c r="B19" s="12"/>
       <c r="C19" s="34"/>
       <c r="D19" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E19" s="54" t="s">
         <v>742</v>
@@ -15034,7 +15031,7 @@
         <v>749</v>
       </c>
       <c r="Q19" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="R19" s="54"/>
       <c r="V19" s="62"/>
@@ -15071,7 +15068,7 @@
       </c>
       <c r="N20" s="56"/>
       <c r="O20" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="P20" s="56" t="s">
         <v>749</v>
@@ -15141,45 +15138,45 @@
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
       <c r="D22" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G22" s="24"/>
       <c r="H22" s="24" t="s">
+        <v>1586</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>966</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>987</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>988</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="M22" s="24" t="s">
         <v>1587</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>967</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>988</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>989</v>
-      </c>
-      <c r="L22" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>1588</v>
       </c>
       <c r="N22" s="24"/>
       <c r="O22" s="24" t="s">
+        <v>992</v>
+      </c>
+      <c r="P22" s="24" t="s">
         <v>993</v>
       </c>
-      <c r="P22" s="24" t="s">
+      <c r="Q22" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="R22" s="24" t="s">
         <v>994</v>
-      </c>
-      <c r="Q22" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="R22" s="24" t="s">
-        <v>995</v>
       </c>
       <c r="S22" s="31"/>
       <c r="V22" s="62"/>
@@ -15191,7 +15188,7 @@
       <c r="E23" s="54"/>
       <c r="F23" s="54"/>
       <c r="G23" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H23" s="54"/>
       <c r="I23" s="54" t="s">
@@ -15204,7 +15201,7 @@
       <c r="N23" s="54"/>
       <c r="O23" s="54"/>
       <c r="P23" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q23" s="54"/>
       <c r="R23" s="54"/>
@@ -15242,7 +15239,7 @@
         <v>194</v>
       </c>
       <c r="O24" s="56" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="P24" s="56" t="s">
         <v>239</v>
@@ -15312,45 +15309,45 @@
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="22"/>
       <c r="D26" s="24" t="s">
+        <v>995</v>
+      </c>
+      <c r="E26" s="24" t="s">
         <v>996</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>997</v>
       </c>
       <c r="F26" s="24"/>
       <c r="G26" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="I26" s="24" t="s">
+        <v>997</v>
+      </c>
+      <c r="J26" s="24" t="s">
+        <v>965</v>
+      </c>
+      <c r="K26" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="L26" s="24" t="s">
         <v>998</v>
-      </c>
-      <c r="J26" s="24" t="s">
-        <v>966</v>
-      </c>
-      <c r="K26" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="L26" s="24" t="s">
-        <v>999</v>
       </c>
       <c r="M26" s="24"/>
       <c r="N26" s="24" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="O26" s="24" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="P26" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="Q26" s="24" t="s">
+        <v>994</v>
+      </c>
+      <c r="R26" s="24" t="s">
         <v>995</v>
-      </c>
-      <c r="R26" s="24" t="s">
-        <v>996</v>
       </c>
       <c r="S26" s="31"/>
       <c r="V26" s="62"/>
@@ -15443,7 +15440,7 @@
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="22"/>
       <c r="D30" s="24" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
@@ -15565,12 +15562,12 @@
       <c r="B35" s="12"/>
       <c r="C35" s="34"/>
       <c r="D35" s="54" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E35" s="54"/>
       <c r="F35" s="54"/>
       <c r="G35" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H35" s="54" t="s">
         <v>244</v>
@@ -15583,7 +15580,7 @@
       </c>
       <c r="M35" s="54"/>
       <c r="N35" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="O35" s="54"/>
       <c r="P35" s="54"/>
@@ -15596,7 +15593,7 @@
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="17"/>
       <c r="D36" s="56" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E36" s="56" t="s">
         <v>220</v>
@@ -15609,17 +15606,17 @@
         <v>244</v>
       </c>
       <c r="I36" s="56" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="J36" s="56" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K36" s="56"/>
       <c r="L36" s="56" t="s">
         <v>217</v>
       </c>
       <c r="M36" s="56" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="N36" s="56" t="s">
         <v>239</v>
@@ -15693,43 +15690,43 @@
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="22"/>
       <c r="D38" s="24" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F38" s="24"/>
       <c r="G38" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="I38" s="24" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J38" s="24" t="s">
         <v>1005</v>
-      </c>
-      <c r="J38" s="24" t="s">
-        <v>1006</v>
       </c>
       <c r="K38" s="24"/>
       <c r="L38" s="24" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="M38" s="24" t="s">
+        <v>1007</v>
+      </c>
+      <c r="N38" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O38" s="24" t="s">
+        <v>994</v>
+      </c>
+      <c r="P38" s="24" t="s">
         <v>1008</v>
-      </c>
-      <c r="N38" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O38" s="24" t="s">
-        <v>995</v>
-      </c>
-      <c r="P38" s="24" t="s">
-        <v>1009</v>
       </c>
       <c r="Q38" s="24"/>
       <c r="R38" s="24" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="S38" s="31"/>
       <c r="V38" s="62"/>
@@ -15739,7 +15736,7 @@
       <c r="C39" s="34"/>
       <c r="D39" s="54"/>
       <c r="E39" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F39" s="54"/>
       <c r="G39" s="54"/>
@@ -15749,12 +15746,12 @@
         <v>321</v>
       </c>
       <c r="K39" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L39" s="54"/>
       <c r="M39" s="54"/>
       <c r="N39" s="54" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="O39" s="54"/>
       <c r="P39" s="54" t="s">
@@ -15769,7 +15766,7 @@
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="17"/>
       <c r="D40" s="56" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E40" s="56" t="s">
         <v>239</v>
@@ -15785,29 +15782,29 @@
         <v>220</v>
       </c>
       <c r="J40" s="56" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="K40" s="56" t="s">
+        <v>807</v>
+      </c>
+      <c r="L40" s="56" t="s">
         <v>808</v>
-      </c>
-      <c r="L40" s="56" t="s">
-        <v>809</v>
       </c>
       <c r="M40" s="56"/>
       <c r="N40" s="56" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="O40" s="56" t="s">
         <v>265</v>
       </c>
       <c r="P40" s="56" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="Q40" s="56" t="s">
         <v>270</v>
       </c>
       <c r="R40" s="56" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="S40" s="19"/>
       <c r="V40" s="62"/>
@@ -15868,45 +15865,45 @@
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="22"/>
       <c r="D42" s="24" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>994</v>
+      </c>
+      <c r="G42" s="24" t="s">
         <v>1011</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="F42" s="24" t="s">
-        <v>995</v>
-      </c>
-      <c r="G42" s="24" t="s">
-        <v>1012</v>
       </c>
       <c r="H42" s="24"/>
       <c r="I42" s="24" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="J42" s="24" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="K42" s="24" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="M42" s="24"/>
       <c r="N42" s="24" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="O42" s="24" t="s">
+        <v>1013</v>
+      </c>
+      <c r="P42" s="24" t="s">
         <v>1014</v>
       </c>
-      <c r="P42" s="24" t="s">
+      <c r="Q42" s="24" t="s">
+        <v>1011</v>
+      </c>
+      <c r="R42" s="24" t="s">
         <v>1015</v>
-      </c>
-      <c r="Q42" s="24" t="s">
-        <v>1012</v>
-      </c>
-      <c r="R42" s="24" t="s">
-        <v>1016</v>
       </c>
       <c r="S42" s="31"/>
       <c r="V42" s="62"/>
@@ -15921,7 +15918,7 @@
         <v>604</v>
       </c>
       <c r="H43" s="54" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I43" s="54"/>
       <c r="J43" s="54"/>
@@ -15931,7 +15928,7 @@
       </c>
       <c r="M43" s="54"/>
       <c r="N43" s="54" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="O43" s="54"/>
       <c r="P43" s="54"/>
@@ -15942,39 +15939,39 @@
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="17"/>
       <c r="D44" s="56" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E44" s="56"/>
       <c r="F44" s="56" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G44" s="56" t="s">
         <v>701</v>
       </c>
       <c r="H44" s="56" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I44" s="56" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J44" s="56"/>
       <c r="K44" s="56" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="L44" s="56" t="s">
         <v>264</v>
       </c>
       <c r="M44" s="56" t="s">
+        <v>817</v>
+      </c>
+      <c r="N44" s="56" t="s">
+        <v>1564</v>
+      </c>
+      <c r="O44" s="56" t="s">
         <v>818</v>
       </c>
-      <c r="N44" s="56" t="s">
-        <v>1565</v>
-      </c>
-      <c r="O44" s="56" t="s">
-        <v>819</v>
-      </c>
       <c r="P44" s="56" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="Q44" s="56"/>
       <c r="R44" s="56"/>
@@ -16014,7 +16011,7 @@
         <v>354</v>
       </c>
       <c r="M45" s="41" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N45" s="41" t="s">
         <v>60</v>
@@ -16039,39 +16036,39 @@
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="22"/>
       <c r="D46" s="24" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E46" s="24"/>
       <c r="F46" s="24" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G46" s="24" t="s">
         <v>1018</v>
       </c>
-      <c r="G46" s="24" t="s">
+      <c r="H46" s="24" t="s">
         <v>1019</v>
       </c>
-      <c r="H46" s="24" t="s">
+      <c r="I46" s="24" t="s">
         <v>1020</v>
-      </c>
-      <c r="I46" s="24" t="s">
-        <v>1021</v>
       </c>
       <c r="J46" s="24"/>
       <c r="K46" s="24" t="s">
+        <v>1021</v>
+      </c>
+      <c r="L46" s="24" t="s">
+        <v>1583</v>
+      </c>
+      <c r="M46" s="24" t="s">
         <v>1022</v>
       </c>
-      <c r="L46" s="24" t="s">
-        <v>1584</v>
-      </c>
-      <c r="M46" s="24" t="s">
+      <c r="N46" s="24" t="s">
+        <v>1590</v>
+      </c>
+      <c r="O46" s="24" t="s">
         <v>1023</v>
       </c>
-      <c r="N46" s="24" t="s">
-        <v>1591</v>
-      </c>
-      <c r="O46" s="24" t="s">
+      <c r="P46" s="24" t="s">
         <v>1024</v>
-      </c>
-      <c r="P46" s="24" t="s">
-        <v>1025</v>
       </c>
       <c r="Q46" s="24"/>
       <c r="R46" s="24"/>
@@ -16177,7 +16174,7 @@
       <c r="J51" s="54"/>
       <c r="K51" s="54"/>
       <c r="L51" s="54" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="M51" s="54"/>
       <c r="N51" s="54"/>
@@ -16190,39 +16187,39 @@
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="17"/>
       <c r="D52" s="56" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E52" s="56" t="s">
         <v>266</v>
       </c>
       <c r="F52" s="56" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G52" s="56" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H52" s="56"/>
       <c r="I52" s="56" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J52" s="56" t="s">
         <v>194</v>
       </c>
       <c r="K52" s="56" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L52" s="56" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="M52" s="56" t="s">
         <v>222</v>
       </c>
       <c r="N52" s="56" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O52" s="56"/>
       <c r="P52" s="56" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="Q52" s="56" t="s">
         <v>234</v>
@@ -16289,45 +16286,45 @@
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="22"/>
       <c r="D54" s="24" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E54" s="24" t="s">
         <v>1026</v>
       </c>
-      <c r="E54" s="24" t="s">
-        <v>1027</v>
-      </c>
       <c r="F54" s="24" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="G54" s="24" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H54" s="24"/>
       <c r="I54" s="24" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J54" s="24" t="s">
+        <v>985</v>
+      </c>
+      <c r="K54" s="24" t="s">
         <v>1034</v>
       </c>
-      <c r="J54" s="24" t="s">
-        <v>986</v>
-      </c>
-      <c r="K54" s="24" t="s">
+      <c r="L54" s="24" t="s">
+        <v>1591</v>
+      </c>
+      <c r="M54" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="N54" s="24" t="s">
         <v>1035</v>
-      </c>
-      <c r="L54" s="24" t="s">
-        <v>1592</v>
-      </c>
-      <c r="M54" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="N54" s="24" t="s">
-        <v>1036</v>
       </c>
       <c r="O54" s="24"/>
       <c r="P54" s="24" t="s">
+        <v>1036</v>
+      </c>
+      <c r="Q54" s="24" t="s">
         <v>1037</v>
       </c>
-      <c r="Q54" s="24" t="s">
+      <c r="R54" s="24" t="s">
         <v>1038</v>
-      </c>
-      <c r="R54" s="24" t="s">
-        <v>1039</v>
       </c>
       <c r="S54" s="31"/>
       <c r="V54" s="62"/>
@@ -16361,43 +16358,43 @@
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="17"/>
       <c r="D56" s="56" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E56" s="56"/>
       <c r="F56" s="56" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G56" s="56" t="s">
         <v>280</v>
       </c>
       <c r="H56" s="56" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I56" s="56" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J56" s="56" t="s">
         <v>222</v>
       </c>
       <c r="K56" s="56" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="L56" s="56"/>
       <c r="M56" s="56" t="s">
+        <v>828</v>
+      </c>
+      <c r="N56" s="56" t="s">
         <v>829</v>
       </c>
-      <c r="N56" s="56" t="s">
-        <v>830</v>
-      </c>
       <c r="O56" s="56" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P56" s="56" t="s">
         <v>225</v>
       </c>
       <c r="Q56" s="56"/>
       <c r="R56" s="56" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="S56" s="19"/>
       <c r="V56" s="62"/>
@@ -16458,43 +16455,43 @@
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="22"/>
       <c r="D58" s="24" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E58" s="24"/>
       <c r="F58" s="24" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G58" s="24" t="s">
         <v>1041</v>
       </c>
-      <c r="G58" s="24" t="s">
+      <c r="H58" s="24" t="s">
         <v>1042</v>
       </c>
-      <c r="H58" s="24" t="s">
+      <c r="I58" s="24" t="s">
         <v>1043</v>
       </c>
-      <c r="I58" s="24" t="s">
+      <c r="J58" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="K58" s="24" t="s">
         <v>1044</v>
-      </c>
-      <c r="J58" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="K58" s="24" t="s">
-        <v>1045</v>
       </c>
       <c r="L58" s="24"/>
       <c r="M58" s="24" t="s">
+        <v>1045</v>
+      </c>
+      <c r="N58" s="24" t="s">
         <v>1046</v>
       </c>
-      <c r="N58" s="24" t="s">
-        <v>1047</v>
-      </c>
       <c r="O58" s="24" t="s">
+        <v>1049</v>
+      </c>
+      <c r="P58" s="24" t="s">
         <v>1050</v>
-      </c>
-      <c r="P58" s="24" t="s">
-        <v>1051</v>
       </c>
       <c r="Q58" s="24"/>
       <c r="R58" s="24" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="S58" s="31"/>
       <c r="V58" s="62"/>
@@ -16503,10 +16500,10 @@
       <c r="B59" s="12"/>
       <c r="C59" s="34"/>
       <c r="D59" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E59" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F59" s="54"/>
       <c r="G59" s="54"/>
@@ -16521,7 +16518,7 @@
       <c r="N59" s="54"/>
       <c r="O59" s="54"/>
       <c r="P59" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q59" s="54"/>
       <c r="R59" s="54" t="s">
@@ -16551,7 +16548,7 @@
         <v>275</v>
       </c>
       <c r="K60" s="56" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="L60" s="56" t="s">
         <v>267</v>
@@ -16561,7 +16558,7 @@
       </c>
       <c r="N60" s="56"/>
       <c r="O60" s="56" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P60" s="56" t="s">
         <v>244</v>
@@ -16570,7 +16567,7 @@
         <v>235</v>
       </c>
       <c r="R60" s="56" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="S60" s="19"/>
       <c r="V60" s="62"/>
@@ -16631,45 +16628,45 @@
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="22"/>
       <c r="D62" s="24" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="F62" s="24" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="H62" s="24" t="s">
         <v>1053</v>
-      </c>
-      <c r="G62" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="H62" s="24" t="s">
-        <v>1054</v>
       </c>
       <c r="I62" s="24"/>
       <c r="J62" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K62" s="24" t="s">
         <v>1055</v>
       </c>
-      <c r="K62" s="24" t="s">
+      <c r="L62" s="24" t="s">
         <v>1056</v>
       </c>
-      <c r="L62" s="24" t="s">
+      <c r="M62" s="24" t="s">
         <v>1057</v>
-      </c>
-      <c r="M62" s="24" t="s">
-        <v>1058</v>
       </c>
       <c r="N62" s="24"/>
       <c r="O62" s="24" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P62" s="24" t="s">
+        <v>1104</v>
+      </c>
+      <c r="Q62" s="24" t="s">
         <v>1059</v>
       </c>
-      <c r="P62" s="24" t="s">
-        <v>1105</v>
-      </c>
-      <c r="Q62" s="24" t="s">
+      <c r="R62" s="24" t="s">
         <v>1060</v>
-      </c>
-      <c r="R62" s="24" t="s">
-        <v>1061</v>
       </c>
       <c r="S62" s="31"/>
       <c r="V62" s="62"/>
@@ -16756,10 +16753,10 @@
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="22"/>
       <c r="D66" s="24" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F66" s="24"/>
       <c r="G66" s="24"/>
@@ -16868,10 +16865,10 @@
       <c r="B71" s="12"/>
       <c r="C71" s="34"/>
       <c r="D71" s="54" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E71" s="54" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F71" s="54"/>
       <c r="G71" s="54"/>
@@ -16879,7 +16876,7 @@
       <c r="I71" s="54"/>
       <c r="J71" s="54"/>
       <c r="K71" s="54" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L71" s="54"/>
       <c r="M71" s="54" t="s">
@@ -16897,26 +16894,26 @@
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="17"/>
       <c r="D72" s="56" t="s">
+        <v>832</v>
+      </c>
+      <c r="E72" s="56" t="s">
+        <v>938</v>
+      </c>
+      <c r="F72" s="56" t="s">
         <v>833</v>
-      </c>
-      <c r="E72" s="56" t="s">
-        <v>939</v>
-      </c>
-      <c r="F72" s="56" t="s">
-        <v>834</v>
       </c>
       <c r="G72" s="56" t="s">
         <v>280</v>
       </c>
       <c r="H72" s="56" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I72" s="56" t="s">
         <v>198</v>
       </c>
       <c r="J72" s="56"/>
       <c r="K72" s="56" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L72" s="56" t="s">
         <v>207</v>
@@ -16928,14 +16925,14 @@
         <v>277</v>
       </c>
       <c r="O72" s="56" t="s">
+        <v>835</v>
+      </c>
+      <c r="P72" s="56" t="s">
         <v>836</v>
-      </c>
-      <c r="P72" s="56" t="s">
-        <v>837</v>
       </c>
       <c r="Q72" s="56"/>
       <c r="R72" s="56" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="S72" s="19"/>
       <c r="V72" s="62"/>
@@ -16973,10 +16970,10 @@
         <v>101</v>
       </c>
       <c r="M73" s="41" t="s">
+        <v>954</v>
+      </c>
+      <c r="N73" s="41" t="s">
         <v>955</v>
-      </c>
-      <c r="N73" s="41" t="s">
-        <v>956</v>
       </c>
       <c r="O73" s="41" t="s">
         <v>667</v>
@@ -16996,45 +16993,45 @@
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="22"/>
       <c r="D74" s="24" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F74" s="24" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G74" s="24" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H74" s="24" t="s">
         <v>1062</v>
       </c>
-      <c r="G74" s="24" t="s">
-        <v>1042</v>
-      </c>
-      <c r="H74" s="24" t="s">
+      <c r="I74" s="24" t="s">
         <v>1063</v>
-      </c>
-      <c r="I74" s="24" t="s">
-        <v>1064</v>
       </c>
       <c r="J74" s="24"/>
       <c r="K74" s="24" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="L74" s="24" t="s">
+        <v>1064</v>
+      </c>
+      <c r="M74" s="24" t="s">
+        <v>1191</v>
+      </c>
+      <c r="N74" s="24" t="s">
         <v>1065</v>
       </c>
-      <c r="M74" s="24" t="s">
-        <v>1192</v>
-      </c>
-      <c r="N74" s="24" t="s">
+      <c r="O74" s="24" t="s">
         <v>1066</v>
       </c>
-      <c r="O74" s="24" t="s">
+      <c r="P74" s="24" t="s">
         <v>1067</v>
-      </c>
-      <c r="P74" s="24" t="s">
-        <v>1068</v>
       </c>
       <c r="Q74" s="24"/>
       <c r="R74" s="24" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="S74" s="31"/>
       <c r="V74" s="62"/>
@@ -17043,12 +17040,12 @@
       <c r="B75" s="12"/>
       <c r="C75" s="34"/>
       <c r="D75" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E75" s="54"/>
       <c r="F75" s="54"/>
       <c r="G75" s="54" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H75" s="54" t="s">
         <v>341</v>
@@ -17062,11 +17059,11 @@
       <c r="M75" s="54"/>
       <c r="N75" s="54"/>
       <c r="O75" s="54" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P75" s="54"/>
       <c r="Q75" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="R75" s="54"/>
       <c r="V75" s="62"/>
@@ -17077,13 +17074,13 @@
         <v>201</v>
       </c>
       <c r="E76" s="56" t="s">
+        <v>837</v>
+      </c>
+      <c r="F76" s="56" t="s">
+        <v>991</v>
+      </c>
+      <c r="G76" s="56" t="s">
         <v>838</v>
-      </c>
-      <c r="F76" s="56" t="s">
-        <v>992</v>
-      </c>
-      <c r="G76" s="56" t="s">
-        <v>839</v>
       </c>
       <c r="H76" s="56" t="s">
         <v>733</v>
@@ -17096,23 +17093,23 @@
         <v>219</v>
       </c>
       <c r="L76" s="56" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="M76" s="56" t="s">
         <v>255</v>
       </c>
       <c r="N76" s="56" t="s">
+        <v>840</v>
+      </c>
+      <c r="O76" s="56" t="s">
         <v>841</v>
-      </c>
-      <c r="O76" s="56" t="s">
-        <v>842</v>
       </c>
       <c r="P76" s="56"/>
       <c r="Q76" s="56" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="R76" s="56" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="S76" s="19"/>
       <c r="V76" s="62"/>
@@ -17173,45 +17170,45 @@
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="22"/>
       <c r="D78" s="24" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="F78" s="24" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="G78" s="24" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="I78" s="24"/>
       <c r="J78" s="24" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="K78" s="24" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L78" s="24" t="s">
+        <v>1070</v>
+      </c>
+      <c r="M78" s="24" t="s">
+        <v>1071</v>
+      </c>
+      <c r="N78" s="24" t="s">
+        <v>1072</v>
+      </c>
+      <c r="O78" s="24" t="s">
         <v>1597</v>
-      </c>
-      <c r="L78" s="24" t="s">
-        <v>1071</v>
-      </c>
-      <c r="M78" s="24" t="s">
-        <v>1072</v>
-      </c>
-      <c r="N78" s="24" t="s">
-        <v>1073</v>
-      </c>
-      <c r="O78" s="24" t="s">
-        <v>1598</v>
       </c>
       <c r="P78" s="24"/>
       <c r="Q78" s="24" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="R78" s="24" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="S78" s="31"/>
       <c r="V78" s="62"/>
@@ -17220,7 +17217,7 @@
       <c r="B79" s="12"/>
       <c r="C79" s="34"/>
       <c r="D79" s="54" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E79" s="54"/>
       <c r="F79" s="54" t="s">
@@ -17230,7 +17227,7 @@
       <c r="H79" s="54"/>
       <c r="I79" s="54"/>
       <c r="J79" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K79" s="54"/>
       <c r="L79" s="54"/>
@@ -17245,16 +17242,16 @@
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="17"/>
       <c r="D80" s="56" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E80" s="56" t="s">
         <v>258</v>
       </c>
       <c r="F80" s="56" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G80" s="56" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H80" s="56"/>
       <c r="I80" s="56" t="s">
@@ -17267,7 +17264,7 @@
         <v>218</v>
       </c>
       <c r="L80" s="56" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M80" s="56" t="s">
         <v>279</v>
@@ -17336,35 +17333,35 @@
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="22"/>
       <c r="D82" s="24" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="E82" s="24" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F82" s="24" t="s">
         <v>1074</v>
       </c>
-      <c r="F82" s="24" t="s">
+      <c r="G82" s="24" t="s">
         <v>1075</v>
-      </c>
-      <c r="G82" s="24" t="s">
-        <v>1076</v>
       </c>
       <c r="H82" s="24"/>
       <c r="I82" s="24" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J82" s="24" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="K82" s="24" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L82" s="24" t="s">
         <v>1077</v>
       </c>
-      <c r="L82" s="24" t="s">
+      <c r="M82" s="24" t="s">
         <v>1078</v>
       </c>
-      <c r="M82" s="24" t="s">
+      <c r="N82" s="24" t="s">
         <v>1079</v>
-      </c>
-      <c r="N82" s="24" t="s">
-        <v>1080</v>
       </c>
       <c r="O82" s="24"/>
       <c r="P82" s="24"/>
@@ -17465,7 +17462,7 @@
       <c r="C87" s="34"/>
       <c r="D87" s="54"/>
       <c r="E87" s="54" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="F87" s="54"/>
       <c r="G87" s="54"/>
@@ -17477,7 +17474,7 @@
         <v>516</v>
       </c>
       <c r="M87" s="54" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="N87" s="54"/>
       <c r="O87" s="54"/>
@@ -17494,13 +17491,13 @@
         <v>246</v>
       </c>
       <c r="E88" s="56" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="F88" s="56" t="s">
         <v>254</v>
       </c>
       <c r="G88" s="56" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H88" s="56" t="s">
         <v>249</v>
@@ -17509,24 +17506,24 @@
         <v>222</v>
       </c>
       <c r="J88" s="56" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="K88" s="56"/>
       <c r="L88" s="56" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="M88" s="56" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="N88" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="O88" s="56" t="s">
         <v>240</v>
       </c>
       <c r="P88" s="56"/>
       <c r="Q88" s="56" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R88" s="56" t="s">
         <v>278</v>
@@ -17590,45 +17587,45 @@
     <row r="90" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="22"/>
       <c r="D90" s="24" t="s">
+        <v>988</v>
+      </c>
+      <c r="E90" s="24" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F90" s="24" t="s">
+        <v>966</v>
+      </c>
+      <c r="G90" s="24" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H90" s="24" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I90" s="24" t="s">
         <v>989</v>
       </c>
-      <c r="E90" s="24" t="s">
-        <v>1600</v>
-      </c>
-      <c r="F90" s="24" t="s">
-        <v>967</v>
-      </c>
-      <c r="G90" s="24" t="s">
-        <v>1081</v>
-      </c>
-      <c r="H90" s="24" t="s">
+      <c r="J90" s="24" t="s">
         <v>1082</v>
-      </c>
-      <c r="I90" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="J90" s="24" t="s">
-        <v>1083</v>
       </c>
       <c r="K90" s="24"/>
       <c r="L90" s="24" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M90" s="24" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="N90" s="24" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="O90" s="24" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="P90" s="24"/>
       <c r="Q90" s="24" t="s">
+        <v>1084</v>
+      </c>
+      <c r="R90" s="24" t="s">
         <v>1085</v>
-      </c>
-      <c r="R90" s="24" t="s">
-        <v>1086</v>
       </c>
       <c r="S90" s="31"/>
       <c r="V90" s="7"/>
@@ -17646,10 +17643,10 @@
       <c r="I91" s="54"/>
       <c r="J91" s="54"/>
       <c r="K91" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L91" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="M91" s="54"/>
       <c r="N91" s="54"/>
@@ -17668,13 +17665,13 @@
         <v>696</v>
       </c>
       <c r="F92" s="56" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G92" s="56" t="s">
         <v>222</v>
       </c>
       <c r="H92" s="56" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="I92" s="56"/>
       <c r="J92" s="56" t="s">
@@ -17687,7 +17684,7 @@
         <v>239</v>
       </c>
       <c r="M92" s="56" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="N92" s="56"/>
       <c r="O92" s="56"/>
@@ -17749,32 +17746,32 @@
     <row r="94" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="22"/>
       <c r="D94" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E94" s="24" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F94" s="24" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G94" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="H94" s="24" t="s">
         <v>1087</v>
-      </c>
-      <c r="F94" s="24" t="s">
-        <v>1044</v>
-      </c>
-      <c r="G94" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="H94" s="24" t="s">
-        <v>1088</v>
       </c>
       <c r="I94" s="24"/>
       <c r="J94" s="24" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K94" s="24" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L94" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="M94" s="24" t="s">
         <v>1089</v>
-      </c>
-      <c r="K94" s="24" t="s">
-        <v>1105</v>
-      </c>
-      <c r="L94" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="M94" s="24" t="s">
-        <v>1090</v>
       </c>
       <c r="N94" s="24"/>
       <c r="O94" s="24"/>
@@ -17877,7 +17874,7 @@
       <c r="D99" s="54"/>
       <c r="E99" s="54"/>
       <c r="F99" s="54" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G99" s="54"/>
       <c r="H99" s="54"/>
@@ -17899,13 +17896,13 @@
         <v>345</v>
       </c>
       <c r="E100" s="56" t="s">
+        <v>853</v>
+      </c>
+      <c r="F100" s="56" t="s">
         <v>854</v>
       </c>
-      <c r="F100" s="56" t="s">
-        <v>855</v>
-      </c>
       <c r="G100" s="56" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H100" s="56" t="s">
         <v>222</v>
@@ -17915,7 +17912,7 @@
       </c>
       <c r="J100" s="56"/>
       <c r="K100" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="L100" s="56" t="s">
         <v>226</v>
@@ -17924,10 +17921,10 @@
         <v>243</v>
       </c>
       <c r="N100" s="56" t="s">
+        <v>856</v>
+      </c>
+      <c r="O100" s="56" t="s">
         <v>857</v>
-      </c>
-      <c r="O100" s="56" t="s">
-        <v>858</v>
       </c>
       <c r="P100" s="56"/>
       <c r="Q100" s="56" t="s">
@@ -17995,45 +17992,45 @@
     <row r="102" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B102" s="22"/>
       <c r="D102" s="24" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E102" s="24" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F102" s="24" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G102" s="24" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H102" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="I102" s="24" t="s">
         <v>1091</v>
-      </c>
-      <c r="F102" s="24" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G102" s="24" t="s">
-        <v>1090</v>
-      </c>
-      <c r="H102" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="I102" s="24" t="s">
-        <v>1092</v>
       </c>
       <c r="J102" s="24"/>
       <c r="K102" s="24" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="L102" s="24" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="M102" s="24" t="s">
+        <v>1092</v>
+      </c>
+      <c r="N102" s="24" t="s">
         <v>1093</v>
       </c>
-      <c r="N102" s="24" t="s">
+      <c r="O102" s="24" t="s">
         <v>1094</v>
-      </c>
-      <c r="O102" s="24" t="s">
-        <v>1095</v>
       </c>
       <c r="P102" s="24"/>
       <c r="Q102" s="24" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="R102" s="24" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="S102" s="31"/>
       <c r="V102" s="7"/>
@@ -18065,29 +18062,29 @@
     <row r="104" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B104" s="17"/>
       <c r="D104" s="56" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E104" s="56" t="s">
         <v>227</v>
       </c>
       <c r="F104" s="56"/>
       <c r="G104" s="56" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H104" s="56" t="s">
         <v>215</v>
       </c>
       <c r="I104" s="56" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="J104" s="56" t="s">
         <v>733</v>
       </c>
       <c r="K104" s="56" t="s">
+        <v>858</v>
+      </c>
+      <c r="L104" s="56" t="s">
         <v>859</v>
-      </c>
-      <c r="L104" s="56" t="s">
-        <v>860</v>
       </c>
       <c r="M104" s="56"/>
       <c r="N104" s="56" t="s">
@@ -18100,7 +18097,7 @@
         <v>282</v>
       </c>
       <c r="Q104" s="56" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="R104" s="56"/>
       <c r="S104" s="19"/>
@@ -18162,42 +18159,42 @@
     <row r="106" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B106" s="22"/>
       <c r="D106" s="24" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E106" s="24" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F106" s="24"/>
       <c r="G106" s="24" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H106" s="24" t="s">
         <v>1096</v>
       </c>
-      <c r="H106" s="24" t="s">
+      <c r="I106" s="24" t="s">
+        <v>1093</v>
+      </c>
+      <c r="J106" s="24" t="s">
+        <v>967</v>
+      </c>
+      <c r="K106" s="24" t="s">
         <v>1097</v>
       </c>
-      <c r="I106" s="24" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J106" s="24" t="s">
-        <v>968</v>
-      </c>
-      <c r="K106" s="24" t="s">
+      <c r="L106" s="24" t="s">
         <v>1098</v>
-      </c>
-      <c r="L106" s="24" t="s">
-        <v>1099</v>
       </c>
       <c r="M106" s="24"/>
       <c r="N106" s="24" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O106" s="24" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="P106" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="Q106" s="24" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="R106" s="24"/>
       <c r="S106" s="31"/>
@@ -18208,13 +18205,13 @@
       <c r="C107" s="34"/>
       <c r="D107" s="54"/>
       <c r="E107" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F107" s="54" t="s">
         <v>560</v>
       </c>
       <c r="G107" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H107" s="54"/>
       <c r="I107" s="54"/>
@@ -18232,13 +18229,13 @@
     <row r="108" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B108" s="17"/>
       <c r="D108" s="56" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E108" s="56" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="F108" s="56" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G108" s="56" t="s">
         <v>206</v>
@@ -18247,7 +18244,7 @@
         <v>222</v>
       </c>
       <c r="I108" s="56" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="J108" s="56"/>
       <c r="K108" s="56"/>
@@ -18305,22 +18302,22 @@
     <row r="110" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="22"/>
       <c r="D110" s="24" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E110" s="24" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F110" s="24" t="s">
         <v>1102</v>
       </c>
-      <c r="E110" s="24" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F110" s="24" t="s">
+      <c r="G110" s="24" t="s">
+        <v>1582</v>
+      </c>
+      <c r="H110" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="I110" s="24" t="s">
         <v>1103</v>
-      </c>
-      <c r="G110" s="24" t="s">
-        <v>1583</v>
-      </c>
-      <c r="H110" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="I110" s="24" t="s">
-        <v>1104</v>
       </c>
       <c r="J110" s="24"/>
       <c r="K110" s="24"/>
@@ -18443,11 +18440,11 @@
       <c r="J115" s="54"/>
       <c r="K115" s="54"/>
       <c r="L115" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="M115" s="54"/>
       <c r="N115" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="O115" s="54" t="s">
         <v>250</v>
@@ -18484,10 +18481,10 @@
         <v>254</v>
       </c>
       <c r="L116" s="56" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="M116" s="56" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="N116" s="56" t="s">
         <v>261</v>
@@ -18496,7 +18493,7 @@
         <v>250</v>
       </c>
       <c r="P116" s="56" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="Q116" s="56"/>
       <c r="R116" s="56" t="s">
@@ -18526,7 +18523,7 @@
         <v>116</v>
       </c>
       <c r="I117" s="41" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="J117" s="41" t="s">
         <v>22</v>
@@ -18561,45 +18558,45 @@
     <row r="118" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B118" s="22"/>
       <c r="D118" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E118" s="24" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G118" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H118" s="24" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="I118" s="24" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="J118" s="24"/>
       <c r="K118" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L118" s="24" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="M118" s="24" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="N118" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="O118" s="24" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="P118" s="24" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="Q118" s="24"/>
       <c r="R118" s="24" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="S118" s="31"/>
       <c r="V118" s="7"/>
@@ -18616,16 +18613,16 @@
       </c>
       <c r="G119" s="54"/>
       <c r="H119" s="54" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I119" s="54"/>
       <c r="J119" s="54"/>
       <c r="K119" s="54"/>
       <c r="L119" s="54" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="M119" s="54" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N119" s="54"/>
       <c r="O119" s="54"/>
@@ -18647,17 +18644,17 @@
         <v>220</v>
       </c>
       <c r="F120" s="56" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G120" s="56"/>
       <c r="H120" s="56" t="s">
+        <v>863</v>
+      </c>
+      <c r="I120" s="56" t="s">
         <v>864</v>
       </c>
-      <c r="I120" s="56" t="s">
+      <c r="J120" s="56" t="s">
         <v>865</v>
-      </c>
-      <c r="J120" s="56" t="s">
-        <v>866</v>
       </c>
       <c r="K120" s="56" t="s">
         <v>236</v>
@@ -18666,20 +18663,20 @@
         <v>239</v>
       </c>
       <c r="M120" s="56" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N120" s="56"/>
       <c r="O120" s="56" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="P120" s="56" t="s">
         <v>703</v>
       </c>
       <c r="Q120" s="56" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="R120" s="56" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="S120" s="19"/>
       <c r="V120" s="7"/>
@@ -18740,45 +18737,45 @@
     <row r="122" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B122" s="22"/>
       <c r="D122" s="24" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E122" s="24" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G122" s="24"/>
       <c r="H122" s="24" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="I122" s="24" t="s">
+        <v>1108</v>
+      </c>
+      <c r="J122" s="24" t="s">
         <v>1109</v>
       </c>
-      <c r="J122" s="24" t="s">
+      <c r="K122" s="24" t="s">
         <v>1110</v>
       </c>
-      <c r="K122" s="24" t="s">
+      <c r="L122" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="M122" s="24" t="s">
         <v>1111</v>
-      </c>
-      <c r="L122" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="M122" s="24" t="s">
-        <v>1112</v>
       </c>
       <c r="N122" s="24"/>
       <c r="O122" s="24" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="P122" s="24" t="s">
+        <v>1112</v>
+      </c>
+      <c r="Q122" s="24" t="s">
         <v>1113</v>
       </c>
-      <c r="Q122" s="24" t="s">
+      <c r="R122" s="24" t="s">
         <v>1114</v>
-      </c>
-      <c r="R122" s="24" t="s">
-        <v>1115</v>
       </c>
       <c r="S122" s="31"/>
       <c r="V122" s="7"/>
@@ -18818,13 +18815,13 @@
         <v>738</v>
       </c>
       <c r="H124" s="56" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="I124" s="56" t="s">
         <v>252</v>
       </c>
       <c r="J124" s="56" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K124" s="56"/>
       <c r="L124" s="56"/>
@@ -18884,22 +18881,22 @@
       <c r="B126" s="22"/>
       <c r="D126" s="24"/>
       <c r="E126" s="24" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F126" s="24" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="G126" s="24" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H126" s="24" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I126" s="24" t="s">
         <v>1116</v>
       </c>
-      <c r="I126" s="24" t="s">
+      <c r="J126" s="24" t="s">
         <v>1117</v>
-      </c>
-      <c r="J126" s="24" t="s">
-        <v>1118</v>
       </c>
       <c r="K126" s="24"/>
       <c r="L126" s="24"/>
@@ -19018,7 +19015,7 @@
       <c r="O131" s="57"/>
       <c r="P131" s="57"/>
       <c r="Q131" s="57" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="R131" s="57"/>
       <c r="V131" s="36"/>
@@ -19026,26 +19023,26 @@
     <row r="132" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B132" s="17"/>
       <c r="D132" s="56" t="s">
+        <v>869</v>
+      </c>
+      <c r="E132" s="56" t="s">
+        <v>947</v>
+      </c>
+      <c r="F132" s="56" t="s">
         <v>870</v>
-      </c>
-      <c r="E132" s="56" t="s">
-        <v>948</v>
-      </c>
-      <c r="F132" s="56" t="s">
-        <v>871</v>
       </c>
       <c r="G132" s="56" t="s">
         <v>743</v>
       </c>
       <c r="H132" s="56"/>
       <c r="I132" s="56" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J132" s="56" t="s">
         <v>281</v>
       </c>
       <c r="K132" s="56" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="L132" s="56" t="s">
         <v>277</v>
@@ -19054,14 +19051,14 @@
         <v>258</v>
       </c>
       <c r="N132" s="56" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="O132" s="56"/>
       <c r="P132" s="56" t="s">
         <v>240</v>
       </c>
       <c r="Q132" s="56" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="R132" s="56" t="s">
         <v>258</v>
@@ -19125,45 +19122,45 @@
     <row r="134" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B134" s="22"/>
       <c r="D134" s="24" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E134" s="24" t="s">
         <v>1119</v>
       </c>
-      <c r="E134" s="24" t="s">
+      <c r="F134" s="24" t="s">
         <v>1120</v>
       </c>
-      <c r="F134" s="24" t="s">
+      <c r="G134" s="24" t="s">
         <v>1121</v>
-      </c>
-      <c r="G134" s="24" t="s">
-        <v>1122</v>
       </c>
       <c r="H134" s="24"/>
       <c r="I134" s="24" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="J134" s="24" t="s">
+        <v>1122</v>
+      </c>
+      <c r="K134" s="24" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L134" s="24" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M134" s="24" t="s">
+        <v>1073</v>
+      </c>
+      <c r="N134" s="24" t="s">
         <v>1123</v>
-      </c>
-      <c r="K134" s="24" t="s">
-        <v>1059</v>
-      </c>
-      <c r="L134" s="24" t="s">
-        <v>1066</v>
-      </c>
-      <c r="M134" s="24" t="s">
-        <v>1074</v>
-      </c>
-      <c r="N134" s="24" t="s">
-        <v>1124</v>
       </c>
       <c r="O134" s="24"/>
       <c r="P134" s="24" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="Q134" s="24" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="R134" s="24" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="S134" s="31"/>
       <c r="V134" s="7"/>
@@ -19172,7 +19169,7 @@
       <c r="B135" s="12"/>
       <c r="C135" s="34"/>
       <c r="D135" s="57" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E135" s="57"/>
       <c r="F135" s="57"/>
@@ -19181,11 +19178,11 @@
         <v>586</v>
       </c>
       <c r="I135" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J135" s="57"/>
       <c r="K135" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L135" s="57"/>
       <c r="M135" s="57"/>
@@ -19199,17 +19196,17 @@
     <row r="136" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B136" s="17"/>
       <c r="D136" s="56" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E136" s="56"/>
       <c r="F136" s="56" t="s">
         <v>282</v>
       </c>
       <c r="G136" s="56" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H136" s="56" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="I136" s="56" t="s">
         <v>219</v>
@@ -19278,26 +19275,26 @@
     <row r="138" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B138" s="22"/>
       <c r="D138" s="24" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G138" s="24" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H138" s="24" t="s">
         <v>1125</v>
       </c>
-      <c r="H138" s="24" t="s">
+      <c r="I138" s="24" t="s">
+        <v>1596</v>
+      </c>
+      <c r="J138" s="24" t="s">
         <v>1126</v>
       </c>
-      <c r="I138" s="24" t="s">
-        <v>1597</v>
-      </c>
-      <c r="J138" s="24" t="s">
-        <v>1127</v>
-      </c>
       <c r="K138" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="L138" s="24"/>
       <c r="M138" s="24"/>
@@ -19404,7 +19401,7 @@
         <v>509</v>
       </c>
       <c r="F143" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G143" s="57"/>
       <c r="H143" s="57"/>
@@ -19415,7 +19412,7 @@
         <v>454</v>
       </c>
       <c r="K143" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L143" s="57"/>
       <c r="M143" s="57"/>
@@ -19431,38 +19428,38 @@
     <row r="144" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B144" s="17"/>
       <c r="D144" s="56" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E144" s="56" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F144" s="56" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G144" s="56" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H144" s="56"/>
       <c r="I144" s="56" t="s">
         <v>245</v>
       </c>
       <c r="J144" s="56" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="K144" s="56" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L144" s="56" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="M144" s="56" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="N144" s="56" t="s">
         <v>222</v>
       </c>
       <c r="O144" s="56" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="P144" s="56"/>
       <c r="Q144" s="56" t="s">
@@ -19522,7 +19519,7 @@
         <v>110</v>
       </c>
       <c r="R145" s="41" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="S145" s="21"/>
       <c r="V145" s="7"/>
@@ -19530,45 +19527,45 @@
     <row r="146" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B146" s="22"/>
       <c r="D146" s="24" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E146" s="24" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F146" s="24" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G146" s="24" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H146" s="24"/>
       <c r="I146" s="24" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="J146" s="24" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="K146" s="24" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="L146" s="24" t="s">
+        <v>1131</v>
+      </c>
+      <c r="M146" s="24" t="s">
         <v>1132</v>
       </c>
-      <c r="M146" s="24" t="s">
+      <c r="N146" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="O146" s="24" t="s">
         <v>1133</v>
-      </c>
-      <c r="N146" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="O146" s="24" t="s">
-        <v>1134</v>
       </c>
       <c r="P146" s="24"/>
       <c r="Q146" s="24" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="R146" s="24" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="S146" s="31"/>
       <c r="V146" s="7"/>
@@ -19582,15 +19579,15 @@
       <c r="G147" s="57"/>
       <c r="H147" s="57"/>
       <c r="I147" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J147" s="57"/>
       <c r="K147" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L147" s="57"/>
       <c r="M147" s="57" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="N147" s="57"/>
       <c r="O147" s="57"/>
@@ -19602,23 +19599,23 @@
     <row r="148" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B148" s="17"/>
       <c r="D148" s="56" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E148" s="56" t="s">
         <v>282</v>
       </c>
       <c r="F148" s="56"/>
       <c r="G148" s="56" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H148" s="56" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="I148" s="56" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J148" s="56" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K148" s="56" t="s">
         <v>206</v>
@@ -19627,7 +19624,7 @@
         <v>222</v>
       </c>
       <c r="M148" s="56" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="N148" s="56"/>
       <c r="O148" s="56"/>
@@ -19689,32 +19686,32 @@
     <row r="150" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B150" s="22"/>
       <c r="D150" s="24" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="E150" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F150" s="24"/>
       <c r="G150" s="24" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H150" s="24" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I150" s="24" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="J150" s="24" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="K150" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="L150" s="24" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="M150" s="24" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="N150" s="24"/>
       <c r="O150" s="24"/>
@@ -19839,39 +19836,39 @@
         <v>198</v>
       </c>
       <c r="E156" s="56" t="s">
+        <v>880</v>
+      </c>
+      <c r="F156" s="56" t="s">
         <v>881</v>
       </c>
-      <c r="F156" s="56" t="s">
-        <v>882</v>
-      </c>
       <c r="G156" s="56" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H156" s="56"/>
       <c r="I156" s="56" t="s">
         <v>273</v>
       </c>
       <c r="J156" s="56" t="s">
+        <v>882</v>
+      </c>
+      <c r="K156" s="56" t="s">
         <v>883</v>
       </c>
-      <c r="K156" s="56" t="s">
+      <c r="L156" s="56" t="s">
         <v>884</v>
-      </c>
-      <c r="L156" s="56" t="s">
-        <v>885</v>
       </c>
       <c r="M156" s="56" t="s">
         <v>222</v>
       </c>
       <c r="N156" s="56" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="O156" s="56"/>
       <c r="P156" s="56" t="s">
+        <v>887</v>
+      </c>
+      <c r="Q156" s="56" t="s">
         <v>888</v>
-      </c>
-      <c r="Q156" s="56" t="s">
-        <v>889</v>
       </c>
       <c r="R156" s="56" t="s">
         <v>257</v>
@@ -19935,45 +19932,45 @@
     <row r="158" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B158" s="22"/>
       <c r="D158" s="24" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E158" s="24" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F158" s="24" t="s">
         <v>1137</v>
       </c>
-      <c r="F158" s="24" t="s">
+      <c r="G158" s="24" t="s">
         <v>1138</v>
-      </c>
-      <c r="G158" s="24" t="s">
-        <v>1139</v>
       </c>
       <c r="H158" s="24"/>
       <c r="I158" s="24" t="s">
+        <v>1139</v>
+      </c>
+      <c r="J158" s="24" t="s">
         <v>1140</v>
       </c>
-      <c r="J158" s="24" t="s">
+      <c r="K158" s="24" t="s">
         <v>1141</v>
       </c>
-      <c r="K158" s="24" t="s">
+      <c r="L158" s="24" t="s">
         <v>1142</v>
       </c>
-      <c r="L158" s="24" t="s">
+      <c r="M158" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="N158" s="24" t="s">
         <v>1143</v>
-      </c>
-      <c r="M158" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="N158" s="24" t="s">
-        <v>1144</v>
       </c>
       <c r="O158" s="24"/>
       <c r="P158" s="24" t="s">
+        <v>1144</v>
+      </c>
+      <c r="Q158" s="24" t="s">
         <v>1145</v>
       </c>
-      <c r="Q158" s="24" t="s">
+      <c r="R158" s="24" t="s">
         <v>1146</v>
-      </c>
-      <c r="R158" s="24" t="s">
-        <v>1147</v>
       </c>
       <c r="S158" s="31"/>
       <c r="V158" s="7"/>
@@ -19989,13 +19986,13 @@
       <c r="I159" s="57"/>
       <c r="J159" s="57"/>
       <c r="K159" s="57" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="L159" s="57"/>
       <c r="M159" s="57"/>
       <c r="N159" s="57"/>
       <c r="O159" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="P159" s="57"/>
       <c r="Q159" s="57"/>
@@ -20005,39 +20002,39 @@
     <row r="160" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B160" s="17"/>
       <c r="D160" s="56" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E160" s="56"/>
       <c r="F160" s="56" t="s">
+        <v>890</v>
+      </c>
+      <c r="G160" s="56" t="s">
         <v>891</v>
-      </c>
-      <c r="G160" s="56" t="s">
-        <v>892</v>
       </c>
       <c r="H160" s="56" t="s">
         <v>256</v>
       </c>
       <c r="I160" s="56" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="J160" s="56" t="s">
         <v>222</v>
       </c>
       <c r="K160" s="56" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="L160" s="56"/>
       <c r="M160" s="56" t="s">
         <v>282</v>
       </c>
       <c r="N160" s="56" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="O160" s="56" t="s">
         <v>239</v>
       </c>
       <c r="P160" s="56" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="Q160" s="56"/>
       <c r="R160" s="56" t="s">
@@ -20102,43 +20099,43 @@
     <row r="162" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B162" s="22"/>
       <c r="D162" s="24" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="24" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G162" s="24" t="s">
         <v>1149</v>
       </c>
-      <c r="G162" s="24" t="s">
+      <c r="H162" s="24" t="s">
         <v>1150</v>
       </c>
-      <c r="H162" s="24" t="s">
+      <c r="I162" s="24" t="s">
         <v>1151</v>
       </c>
-      <c r="I162" s="24" t="s">
-        <v>1152</v>
-      </c>
       <c r="J162" s="24" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="K162" s="24" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="L162" s="24"/>
       <c r="M162" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="N162" s="24" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="O162" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="P162" s="24" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="Q162" s="24"/>
       <c r="R162" s="24" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="S162" s="31"/>
       <c r="V162" s="7"/>
@@ -20159,7 +20156,7 @@
       <c r="J163" s="57"/>
       <c r="K163" s="57"/>
       <c r="L163" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="M163" s="57"/>
       <c r="N163" s="57"/>
@@ -20174,10 +20171,10 @@
     <row r="164" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B164" s="17"/>
       <c r="D164" s="56" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E164" s="56" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F164" s="56" t="s">
         <v>346</v>
@@ -20186,7 +20183,7 @@
         <v>203</v>
       </c>
       <c r="H164" s="56" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="I164" s="56"/>
       <c r="J164" s="56" t="s">
@@ -20199,7 +20196,7 @@
         <v>239</v>
       </c>
       <c r="M164" s="56" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="N164" s="56"/>
       <c r="O164" s="56" t="s">
@@ -20209,7 +20206,7 @@
         <v>236</v>
       </c>
       <c r="Q164" s="56" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="R164" s="56" t="s">
         <v>285</v>
@@ -20273,45 +20270,45 @@
     <row r="166" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B166" s="22"/>
       <c r="D166" s="24" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E166" s="24" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F166" s="24" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G166" s="24" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H166" s="24" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="I166" s="24"/>
       <c r="J166" s="24" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K166" s="24" t="s">
         <v>1155</v>
       </c>
-      <c r="K166" s="24" t="s">
+      <c r="L166" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="M166" s="24" t="s">
         <v>1156</v>
-      </c>
-      <c r="L166" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="M166" s="24" t="s">
-        <v>1157</v>
       </c>
       <c r="N166" s="24"/>
       <c r="O166" s="24" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P166" s="24" t="s">
+        <v>1110</v>
+      </c>
+      <c r="Q166" s="24" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R166" s="24" t="s">
         <v>1158</v>
-      </c>
-      <c r="P166" s="24" t="s">
-        <v>1111</v>
-      </c>
-      <c r="Q166" s="24" t="s">
-        <v>1144</v>
-      </c>
-      <c r="R166" s="24" t="s">
-        <v>1159</v>
       </c>
       <c r="S166" s="31"/>
       <c r="V166" s="7"/>
@@ -20320,7 +20317,7 @@
       <c r="B167" s="12"/>
       <c r="C167" s="34"/>
       <c r="D167" s="57" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="E167" s="57"/>
       <c r="F167" s="57"/>
@@ -20336,7 +20333,7 @@
         <v>255</v>
       </c>
       <c r="P167" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q167" s="57" t="s">
         <v>696</v>
@@ -20347,14 +20344,14 @@
       <c r="B168" s="17"/>
       <c r="C168" s="6"/>
       <c r="D168" s="56" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="E168" s="56" t="s">
         <v>230</v>
       </c>
       <c r="F168" s="56"/>
       <c r="G168" s="56" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H168" s="56" t="s">
         <v>346</v>
@@ -20373,7 +20370,7 @@
         <v>236</v>
       </c>
       <c r="N168" s="56" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="O168" s="56" t="s">
         <v>255</v>
@@ -20442,42 +20439,42 @@
       <c r="B170" s="22"/>
       <c r="C170" s="6"/>
       <c r="D170" s="24" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="E170" s="24" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="F170" s="24"/>
       <c r="G170" s="24" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H170" s="24" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="I170" s="24" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="J170" s="24" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="K170" s="24"/>
       <c r="L170" s="24" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="M170" s="24" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="N170" s="24" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="O170" s="24" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="P170" s="24" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="Q170" s="24" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="R170" s="24"/>
     </row>
@@ -20490,11 +20487,11 @@
       </c>
       <c r="F171" s="57"/>
       <c r="G171" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H171" s="57"/>
       <c r="I171" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J171" s="57"/>
       <c r="K171" s="57"/>
@@ -20512,13 +20509,13 @@
       <c r="B172" s="17"/>
       <c r="C172" s="6"/>
       <c r="D172" s="56" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E172" s="56" t="s">
         <v>217</v>
       </c>
       <c r="F172" s="56" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G172" s="56" t="s">
         <v>206</v>
@@ -20528,7 +20525,7 @@
         <v>239</v>
       </c>
       <c r="J172" s="56" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="K172" s="56" t="s">
         <v>346</v>
@@ -20540,7 +20537,7 @@
         <v>258</v>
       </c>
       <c r="N172" s="56" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="O172" s="56"/>
       <c r="P172" s="56"/>
@@ -20601,35 +20598,35 @@
       <c r="B174" s="22"/>
       <c r="C174" s="6"/>
       <c r="D174" s="24" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="E174" s="24" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F174" s="24" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G174" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H174" s="24"/>
       <c r="I174" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="J174" s="24" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K174" s="24" t="s">
+        <v>1009</v>
+      </c>
+      <c r="L174" s="24" t="s">
+        <v>962</v>
+      </c>
+      <c r="M174" s="24" t="s">
+        <v>1073</v>
+      </c>
+      <c r="N174" s="24" t="s">
         <v>1164</v>
-      </c>
-      <c r="K174" s="24" t="s">
-        <v>1010</v>
-      </c>
-      <c r="L174" s="24" t="s">
-        <v>963</v>
-      </c>
-      <c r="M174" s="24" t="s">
-        <v>1074</v>
-      </c>
-      <c r="N174" s="24" t="s">
-        <v>1165</v>
       </c>
       <c r="O174" s="24"/>
       <c r="P174" s="24"/>
@@ -20724,14 +20721,14 @@
       <c r="C179" s="34"/>
       <c r="D179" s="57"/>
       <c r="E179" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F179" s="57"/>
       <c r="G179" s="57"/>
       <c r="H179" s="57"/>
       <c r="I179" s="57"/>
       <c r="J179" s="57" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="K179" s="57"/>
       <c r="L179" s="57" t="s">
@@ -20740,7 +20737,7 @@
       <c r="M179" s="57"/>
       <c r="N179" s="57"/>
       <c r="O179" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="P179" s="57"/>
       <c r="Q179" s="57"/>
@@ -20766,17 +20763,17 @@
         <v>243</v>
       </c>
       <c r="J180" s="56" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="K180" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="L180" s="56" t="s">
         <v>264</v>
       </c>
       <c r="M180" s="56"/>
       <c r="N180" s="56" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O180" s="56" t="s">
         <v>239</v>
@@ -20845,42 +20842,42 @@
       <c r="B182" s="22"/>
       <c r="C182" s="6"/>
       <c r="D182" s="24" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E182" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="F182" s="24" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G182" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H182" s="24"/>
       <c r="I182" s="24" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J182" s="24" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="K182" s="24" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="L182" s="24" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="M182" s="24"/>
       <c r="N182" s="24" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="O182" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="P182" s="24" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="Q182" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="R182" s="24"/>
     </row>
@@ -20894,15 +20891,15 @@
         <v>170</v>
       </c>
       <c r="F183" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G183" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H183" s="57"/>
       <c r="I183" s="57"/>
       <c r="J183" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K183" s="57"/>
       <c r="L183" s="57"/>
@@ -20910,7 +20907,7 @@
       <c r="N183" s="57"/>
       <c r="O183" s="57"/>
       <c r="P183" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q183" s="57"/>
       <c r="R183" s="57"/>
@@ -20919,7 +20916,7 @@
       <c r="B184" s="17"/>
       <c r="C184" s="6"/>
       <c r="D184" s="56" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E184" s="56" t="s">
         <v>260</v>
@@ -20932,7 +20929,7 @@
       </c>
       <c r="H184" s="56"/>
       <c r="I184" s="56" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J184" s="56" t="s">
         <v>239</v>
@@ -20954,7 +20951,7 @@
         <v>239</v>
       </c>
       <c r="Q184" s="56" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R184" s="56"/>
     </row>
@@ -21014,42 +21011,42 @@
       <c r="B186" s="22"/>
       <c r="C186" s="6"/>
       <c r="D186" s="24" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E186" s="24" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F186" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="G186" s="24" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H186" s="24"/>
       <c r="I186" s="24" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="J186" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="K186" s="24" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="L186" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="M186" s="24"/>
       <c r="N186" s="24" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="O186" s="24" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="P186" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="Q186" s="24" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="R186" s="24"/>
     </row>
@@ -21057,10 +21054,10 @@
       <c r="B187" s="12"/>
       <c r="C187" s="34"/>
       <c r="D187" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E187" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F187" s="57"/>
       <c r="G187" s="57"/>
@@ -21070,7 +21067,7 @@
       </c>
       <c r="J187" s="57"/>
       <c r="K187" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L187" s="57"/>
       <c r="M187" s="57"/>
@@ -21097,10 +21094,10 @@
       </c>
       <c r="H188" s="56"/>
       <c r="I188" s="56" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="J188" s="56" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="K188" s="56" t="s">
         <v>239</v>
@@ -21110,13 +21107,13 @@
       </c>
       <c r="M188" s="56"/>
       <c r="N188" s="56" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="O188" s="56" t="s">
         <v>736</v>
       </c>
       <c r="P188" s="56" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="Q188" s="56" t="s">
         <v>702</v>
@@ -21179,42 +21176,42 @@
       <c r="B190" s="22"/>
       <c r="C190" s="6"/>
       <c r="D190" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="E190" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="F190" s="24" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G190" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H190" s="24"/>
       <c r="I190" s="24" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="J190" s="24" t="s">
+        <v>999</v>
+      </c>
+      <c r="K190" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="L190" s="24" t="s">
         <v>1000</v>
-      </c>
-      <c r="K190" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="L190" s="24" t="s">
-        <v>1001</v>
       </c>
       <c r="M190" s="24"/>
       <c r="N190" s="24" t="s">
+        <v>1168</v>
+      </c>
+      <c r="O190" s="24" t="s">
+        <v>974</v>
+      </c>
+      <c r="P190" s="24" t="s">
+        <v>1168</v>
+      </c>
+      <c r="Q190" s="24" t="s">
         <v>1169</v>
-      </c>
-      <c r="O190" s="24" t="s">
-        <v>975</v>
-      </c>
-      <c r="P190" s="24" t="s">
-        <v>1169</v>
-      </c>
-      <c r="Q190" s="24" t="s">
-        <v>1170</v>
       </c>
       <c r="R190" s="24"/>
     </row>
@@ -21222,30 +21219,30 @@
       <c r="B191" s="12"/>
       <c r="C191" s="34"/>
       <c r="D191" s="57" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E191" s="57"/>
       <c r="F191" s="57"/>
       <c r="G191" s="57"/>
       <c r="H191" s="57"/>
       <c r="I191" s="57" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="J191" s="57"/>
       <c r="K191" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L191" s="57"/>
       <c r="M191" s="57"/>
       <c r="N191" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="O191" s="57" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="P191" s="57"/>
       <c r="Q191" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="R191" s="57"/>
     </row>
@@ -21253,7 +21250,7 @@
       <c r="B192" s="17"/>
       <c r="C192" s="6"/>
       <c r="D192" s="56" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E192" s="56" t="s">
         <v>246</v>
@@ -21262,29 +21259,29 @@
         <v>221</v>
       </c>
       <c r="G192" s="56" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H192" s="56" t="s">
         <v>242</v>
       </c>
       <c r="I192" s="56" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="J192" s="56"/>
       <c r="K192" s="56" t="s">
         <v>217</v>
       </c>
       <c r="L192" s="56" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M192" s="56" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="N192" s="56" t="s">
         <v>239</v>
       </c>
       <c r="O192" s="56" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="P192" s="56"/>
       <c r="Q192" s="56" t="s">
@@ -21350,58 +21347,58 @@
       <c r="B194" s="22"/>
       <c r="C194" s="6"/>
       <c r="D194" s="24" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E194" s="24" t="s">
+        <v>988</v>
+      </c>
+      <c r="F194" s="24" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G194" s="24" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H194" s="24" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I194" s="24" t="s">
         <v>1612</v>
-      </c>
-      <c r="E194" s="24" t="s">
-        <v>989</v>
-      </c>
-      <c r="F194" s="24" t="s">
-        <v>1171</v>
-      </c>
-      <c r="G194" s="24" t="s">
-        <v>1152</v>
-      </c>
-      <c r="H194" s="24" t="s">
-        <v>1172</v>
-      </c>
-      <c r="I194" s="24" t="s">
-        <v>1613</v>
       </c>
       <c r="J194" s="24"/>
       <c r="K194" s="24" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="L194" s="24" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="M194" s="24" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="N194" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O194" s="24" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="P194" s="24"/>
       <c r="Q194" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="R194" s="24" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="195" spans="2:18">
       <c r="B195" s="12"/>
       <c r="C195" s="34"/>
       <c r="D195" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E195" s="57"/>
       <c r="F195" s="57"/>
       <c r="G195" s="57"/>
       <c r="H195" s="57" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="I195" s="57"/>
       <c r="J195" s="57"/>
@@ -21411,7 +21408,7 @@
       <c r="N195" s="57"/>
       <c r="O195" s="57"/>
       <c r="P195" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q195" s="57"/>
       <c r="R195" s="57"/>
@@ -21426,20 +21423,20 @@
         <v>198</v>
       </c>
       <c r="F196" s="56" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G196" s="56" t="s">
         <v>258</v>
       </c>
       <c r="H196" s="56" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="I196" s="56" t="s">
         <v>276</v>
       </c>
       <c r="J196" s="56"/>
       <c r="K196" s="56" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="L196" s="56" t="s">
         <v>204</v>
@@ -21454,7 +21451,7 @@
         <v>277</v>
       </c>
       <c r="P196" s="56" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="Q196" s="56"/>
       <c r="R196" s="56"/>
@@ -21517,41 +21514,41 @@
       <c r="B198" s="22"/>
       <c r="C198" s="6"/>
       <c r="D198" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="E198" s="24" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F198" s="24" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G198" s="24" t="s">
+        <v>1073</v>
+      </c>
+      <c r="H198" s="24" t="s">
+        <v>1614</v>
+      </c>
+      <c r="I198" s="24" t="s">
         <v>1176</v>
-      </c>
-      <c r="G198" s="24" t="s">
-        <v>1074</v>
-      </c>
-      <c r="H198" s="24" t="s">
-        <v>1615</v>
-      </c>
-      <c r="I198" s="24" t="s">
-        <v>1177</v>
       </c>
       <c r="J198" s="24"/>
       <c r="K198" s="24" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="L198" s="24" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="M198" s="24" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N198" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="O198" s="24" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="P198" s="24" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="Q198" s="24"/>
       <c r="R198" s="24"/>
@@ -21648,7 +21645,7 @@
       <c r="E203" s="57"/>
       <c r="F203" s="57"/>
       <c r="G203" s="57" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H203" s="57" t="s">
         <v>702</v>
@@ -21669,7 +21666,7 @@
         <v>344</v>
       </c>
       <c r="R203" s="57" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="204" spans="2:18" ht="39.75">
@@ -21679,19 +21676,19 @@
         <v>286</v>
       </c>
       <c r="E204" s="58" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F204" s="58" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G204" s="58" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H204" s="58" t="s">
         <v>702</v>
       </c>
       <c r="I204" s="58" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="J204" s="58"/>
       <c r="K204" s="58" t="s">
@@ -21704,17 +21701,17 @@
         <v>212</v>
       </c>
       <c r="N204" s="58" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O204" s="58"/>
       <c r="P204" s="58" t="s">
         <v>248</v>
       </c>
       <c r="Q204" s="58" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="R204" s="58" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="205" spans="2:18" ht="58.5">
@@ -21730,7 +21727,7 @@
         <v>532</v>
       </c>
       <c r="F205" s="41" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G205" s="42" t="s">
         <v>108</v>
@@ -21773,45 +21770,45 @@
       <c r="B206" s="22"/>
       <c r="C206" s="6"/>
       <c r="D206" s="24" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E206" s="38" t="s">
         <v>1179</v>
       </c>
-      <c r="E206" s="38" t="s">
-        <v>1180</v>
-      </c>
       <c r="F206" s="38" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G206" s="38" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H206" s="38" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="I206" s="38" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="J206" s="38"/>
       <c r="K206" s="38" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L206" s="38" t="s">
         <v>1181</v>
       </c>
-      <c r="L206" s="38" t="s">
-        <v>1182</v>
-      </c>
       <c r="M206" s="38" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="N206" s="38" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="O206" s="38"/>
       <c r="P206" s="38" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Q206" s="38" t="s">
         <v>1183</v>
       </c>
-      <c r="Q206" s="38" t="s">
-        <v>1184</v>
-      </c>
       <c r="R206" s="38" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="207" spans="2:18">
@@ -21824,7 +21821,7 @@
       </c>
       <c r="G207" s="57"/>
       <c r="H207" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I207" s="57"/>
       <c r="J207" s="57" t="s">
@@ -21834,11 +21831,11 @@
       <c r="L207" s="57"/>
       <c r="M207" s="57"/>
       <c r="N207" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="O207" s="57"/>
       <c r="P207" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="Q207" s="57"/>
       <c r="R207" s="57"/>
@@ -21847,7 +21844,7 @@
       <c r="B208" s="17"/>
       <c r="C208" s="6"/>
       <c r="D208" s="56" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E208" s="56"/>
       <c r="F208" s="56" t="s">
@@ -21860,7 +21857,7 @@
         <v>239</v>
       </c>
       <c r="I208" s="56" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="J208" s="56" t="s">
         <v>272</v>
@@ -21869,7 +21866,7 @@
         <v>213</v>
       </c>
       <c r="L208" s="56" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="M208" s="56"/>
       <c r="N208" s="56" t="s">
@@ -21882,7 +21879,7 @@
         <v>239</v>
       </c>
       <c r="Q208" s="56" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="R208" s="56" t="s">
         <v>214</v>
@@ -21944,45 +21941,45 @@
       <c r="B210" s="22"/>
       <c r="C210" s="6"/>
       <c r="D210" s="24" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E210" s="24"/>
       <c r="F210" s="24" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G210" s="24" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H210" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="I210" s="24" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J210" s="24" t="s">
         <v>1186</v>
       </c>
-      <c r="J210" s="24" t="s">
+      <c r="K210" s="24" t="s">
         <v>1187</v>
       </c>
-      <c r="K210" s="24" t="s">
-        <v>1188</v>
-      </c>
       <c r="L210" s="24" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="M210" s="24"/>
       <c r="N210" s="24" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="O210" s="24" t="s">
+        <v>1188</v>
+      </c>
+      <c r="P210" s="24" t="s">
+        <v>1581</v>
+      </c>
+      <c r="Q210" s="24" t="s">
+        <v>1185</v>
+      </c>
+      <c r="R210" s="24" t="s">
         <v>1189</v>
-      </c>
-      <c r="P210" s="24" t="s">
-        <v>1582</v>
-      </c>
-      <c r="Q210" s="24" t="s">
-        <v>1186</v>
-      </c>
-      <c r="R210" s="24" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="211" spans="2:18">
@@ -21993,26 +21990,26 @@
       <c r="F211" s="57"/>
       <c r="G211" s="57"/>
       <c r="H211" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I211" s="57"/>
       <c r="J211" s="57"/>
       <c r="K211" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L211" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="M211" s="57"/>
       <c r="N211" s="57"/>
       <c r="O211" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="P211" s="57" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="Q211" s="57" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R211" s="57"/>
     </row>
@@ -22037,26 +22034,26 @@
       </c>
       <c r="J212" s="56"/>
       <c r="K212" s="56" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="L212" s="56" t="s">
         <v>206</v>
       </c>
       <c r="M212" s="56" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="N212" s="56"/>
       <c r="O212" s="56" t="s">
         <v>206</v>
       </c>
       <c r="P212" s="56" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="Q212" s="56" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R212" s="56" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="213" spans="2:18" ht="58.5">
@@ -22081,7 +22078,7 @@
         <v>32</v>
       </c>
       <c r="I213" s="41" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="J213" s="41" t="s">
         <v>22</v>
@@ -22115,43 +22112,43 @@
       <c r="B214" s="22"/>
       <c r="C214" s="6"/>
       <c r="D214" s="24" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E214" s="24" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F214" s="24"/>
       <c r="G214" s="24" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H214" s="24" t="s">
+        <v>1582</v>
+      </c>
+      <c r="I214" s="24" t="s">
         <v>1191</v>
-      </c>
-      <c r="H214" s="24" t="s">
-        <v>1583</v>
-      </c>
-      <c r="I214" s="24" t="s">
-        <v>1192</v>
       </c>
       <c r="J214" s="24"/>
       <c r="K214" s="24" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="L214" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="M214" s="24" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="N214" s="24"/>
       <c r="O214" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="P214" s="24" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q214" s="24" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="R214" s="24" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="215" spans="2:18">
@@ -22160,14 +22157,14 @@
       <c r="D215" s="57"/>
       <c r="E215" s="57"/>
       <c r="F215" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G215" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H215" s="57"/>
       <c r="I215" s="57" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="J215" s="57"/>
       <c r="K215" s="57"/>
@@ -22187,7 +22184,7 @@
         <v>194</v>
       </c>
       <c r="F216" s="56" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G216" s="56" t="s">
         <v>239</v>
@@ -22196,7 +22193,7 @@
         <v>230</v>
       </c>
       <c r="I216" s="56" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="J216" s="56"/>
       <c r="K216" s="56"/>
@@ -22253,19 +22250,19 @@
       <c r="C218" s="6"/>
       <c r="D218" s="24"/>
       <c r="E218" s="24" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F218" s="24" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="G218" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H218" s="24" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="I218" s="24" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="J218" s="24"/>
       <c r="K218" s="24"/>
@@ -22407,17 +22404,17 @@
         <v>237</v>
       </c>
       <c r="L224" s="56" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="M224" s="56"/>
       <c r="N224" s="56" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="O224" s="56" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="P224" s="56" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="Q224" s="56" t="s">
         <v>264</v>
@@ -22480,42 +22477,42 @@
       <c r="B226" s="22"/>
       <c r="C226" s="6"/>
       <c r="D226" s="24" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E226" s="24" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F226" s="24" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G226" s="24" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H226" s="24"/>
       <c r="I226" s="24" t="s">
+        <v>1194</v>
+      </c>
+      <c r="J226" s="24" t="s">
+        <v>998</v>
+      </c>
+      <c r="K226" s="24" t="s">
         <v>1195</v>
       </c>
-      <c r="J226" s="24" t="s">
-        <v>999</v>
-      </c>
-      <c r="K226" s="24" t="s">
+      <c r="L226" s="24" t="s">
         <v>1196</v>
-      </c>
-      <c r="L226" s="24" t="s">
-        <v>1197</v>
       </c>
       <c r="M226" s="24"/>
       <c r="N226" s="24" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="O226" s="24" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="P226" s="24" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="Q226" s="24" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="R226" s="24"/>
     </row>
@@ -22527,24 +22524,24 @@
       <c r="F227" s="57"/>
       <c r="G227" s="57"/>
       <c r="H227" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I227" s="57"/>
       <c r="J227" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K227" s="57"/>
       <c r="L227" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="M227" s="57"/>
       <c r="N227" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="O227" s="57"/>
       <c r="P227" s="57"/>
       <c r="Q227" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="R227" s="57"/>
     </row>
@@ -22552,19 +22549,19 @@
       <c r="B228" s="17"/>
       <c r="C228" s="6"/>
       <c r="D228" s="56" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E228" s="56" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F228" s="56" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G228" s="56" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H228" s="56" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="I228" s="56" t="s">
         <v>226</v>
@@ -22576,20 +22573,20 @@
         <v>222</v>
       </c>
       <c r="L228" s="56" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="M228" s="56"/>
       <c r="N228" s="56" t="s">
         <v>261</v>
       </c>
       <c r="O228" s="56" t="s">
+        <v>913</v>
+      </c>
+      <c r="P228" s="56" t="s">
         <v>914</v>
       </c>
-      <c r="P228" s="56" t="s">
-        <v>915</v>
-      </c>
       <c r="Q228" s="56" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="R228" s="56" t="s">
         <v>232</v>
@@ -22651,47 +22648,47 @@
       <c r="B230" s="22"/>
       <c r="C230" s="6"/>
       <c r="D230" s="24" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="E230" s="24" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F230" s="24" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G230" s="24" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H230" s="24" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="I230" s="24" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="J230" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="K230" s="24" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="L230" s="24" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="M230" s="24"/>
       <c r="N230" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="O230" s="24" t="s">
+        <v>1199</v>
+      </c>
+      <c r="P230" s="24" t="s">
         <v>1200</v>
       </c>
-      <c r="P230" s="24" t="s">
-        <v>1201</v>
-      </c>
       <c r="Q230" s="24" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="R230" s="24" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="231" spans="2:18">
@@ -22699,17 +22696,17 @@
       <c r="C231" s="34"/>
       <c r="D231" s="57"/>
       <c r="E231" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F231" s="57"/>
       <c r="G231" s="57" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H231" s="57"/>
       <c r="I231" s="57"/>
       <c r="J231" s="57"/>
       <c r="K231" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L231" s="57"/>
       <c r="M231" s="57"/>
@@ -22734,20 +22731,20 @@
         <v>222</v>
       </c>
       <c r="G232" s="56" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H232" s="56"/>
       <c r="I232" s="56" t="s">
         <v>254</v>
       </c>
       <c r="J232" s="56" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="K232" s="56" t="s">
         <v>208</v>
       </c>
       <c r="L232" s="56" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M232" s="56" t="s">
         <v>222</v>
@@ -22760,10 +22757,10 @@
         <v>254</v>
       </c>
       <c r="Q232" s="56" t="s">
+        <v>916</v>
+      </c>
+      <c r="R232" s="56" t="s">
         <v>917</v>
-      </c>
-      <c r="R232" s="56" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="233" spans="2:18" ht="58.5">
@@ -22822,45 +22819,45 @@
       <c r="B234" s="22"/>
       <c r="C234" s="6"/>
       <c r="D234" s="24" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="E234" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F234" s="24" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G234" s="24" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H234" s="24"/>
       <c r="I234" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="J234" s="24" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K234" s="24" t="s">
+        <v>1584</v>
+      </c>
+      <c r="L234" s="24" t="s">
         <v>1203</v>
       </c>
-      <c r="K234" s="24" t="s">
-        <v>1585</v>
-      </c>
-      <c r="L234" s="24" t="s">
-        <v>1204</v>
-      </c>
       <c r="M234" s="24" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="N234" s="24" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="O234" s="24"/>
       <c r="P234" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="Q234" s="24" t="s">
+        <v>1204</v>
+      </c>
+      <c r="R234" s="24" t="s">
         <v>1205</v>
-      </c>
-      <c r="R234" s="24" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="235" spans="2:18">
@@ -22871,11 +22868,11 @@
       <c r="F235" s="57"/>
       <c r="G235" s="57"/>
       <c r="H235" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I235" s="57"/>
       <c r="J235" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K235" s="57"/>
       <c r="L235" s="57"/>
@@ -22886,7 +22883,7 @@
       </c>
       <c r="P235" s="57"/>
       <c r="Q235" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="R235" s="57"/>
     </row>
@@ -22894,13 +22891,13 @@
       <c r="B236" s="17"/>
       <c r="C236" s="6"/>
       <c r="D236" s="56" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E236" s="56" t="s">
         <v>222</v>
       </c>
       <c r="F236" s="56" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G236" s="56"/>
       <c r="H236" s="56" t="s">
@@ -22916,16 +22913,16 @@
         <v>254</v>
       </c>
       <c r="L236" s="56" t="s">
+        <v>920</v>
+      </c>
+      <c r="M236" s="56" t="s">
         <v>921</v>
-      </c>
-      <c r="M236" s="56" t="s">
-        <v>922</v>
       </c>
       <c r="N236" s="56" t="s">
         <v>232</v>
       </c>
       <c r="O236" s="56" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="P236" s="56"/>
       <c r="Q236" s="56" t="s">
@@ -22991,58 +22988,58 @@
       <c r="B238" s="22"/>
       <c r="C238" s="6"/>
       <c r="D238" s="24" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E238" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="F238" s="24" t="s">
         <v>1207</v>
-      </c>
-      <c r="E238" s="24" t="s">
-        <v>990</v>
-      </c>
-      <c r="F238" s="24" t="s">
-        <v>1208</v>
       </c>
       <c r="G238" s="24"/>
       <c r="H238" s="24" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="I238" s="24" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="J238" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="K238" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L238" s="24" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M238" s="24" t="s">
         <v>1209</v>
       </c>
-      <c r="M238" s="24" t="s">
+      <c r="N238" s="24" t="s">
+        <v>987</v>
+      </c>
+      <c r="O238" s="24" t="s">
         <v>1210</v>
-      </c>
-      <c r="N238" s="24" t="s">
-        <v>988</v>
-      </c>
-      <c r="O238" s="24" t="s">
-        <v>1211</v>
       </c>
       <c r="P238" s="24"/>
       <c r="Q238" s="24" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="R238" s="24" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="239" spans="2:18">
       <c r="B239" s="12"/>
       <c r="C239" s="34"/>
       <c r="D239" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E239" s="57"/>
       <c r="F239" s="57"/>
       <c r="G239" s="57"/>
       <c r="H239" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I239" s="57"/>
       <c r="J239" s="57"/>
@@ -23065,7 +23062,7 @@
         <v>254</v>
       </c>
       <c r="F240" s="56" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G240" s="56" t="s">
         <v>211</v>
@@ -23074,30 +23071,30 @@
         <v>208</v>
       </c>
       <c r="I240" s="56" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J240" s="56"/>
       <c r="K240" s="56" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L240" s="56" t="s">
         <v>234</v>
       </c>
       <c r="M240" s="56" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="N240" s="56" t="s">
+        <v>924</v>
+      </c>
+      <c r="O240" s="56" t="s">
         <v>925</v>
       </c>
-      <c r="O240" s="56" t="s">
+      <c r="P240" s="56" t="s">
         <v>926</v>
-      </c>
-      <c r="P240" s="56" t="s">
-        <v>927</v>
       </c>
       <c r="Q240" s="56"/>
       <c r="R240" s="56" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="241" spans="2:18" ht="58.5">
@@ -23156,45 +23153,45 @@
       <c r="B242" s="22"/>
       <c r="C242" s="6"/>
       <c r="D242" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E242" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F242" s="24" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G242" s="24" t="s">
         <v>1212</v>
       </c>
-      <c r="G242" s="24" t="s">
+      <c r="H242" s="24" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I242" s="24" t="s">
         <v>1213</v>
-      </c>
-      <c r="H242" s="24" t="s">
-        <v>1585</v>
-      </c>
-      <c r="I242" s="24" t="s">
-        <v>1214</v>
       </c>
       <c r="J242" s="24"/>
       <c r="K242" s="24" t="s">
+        <v>1214</v>
+      </c>
+      <c r="L242" s="24" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M242" s="24" t="s">
+        <v>1105</v>
+      </c>
+      <c r="N242" s="24" t="s">
         <v>1215</v>
       </c>
-      <c r="L242" s="24" t="s">
-        <v>1038</v>
-      </c>
-      <c r="M242" s="24" t="s">
-        <v>1106</v>
-      </c>
-      <c r="N242" s="24" t="s">
+      <c r="O242" s="24" t="s">
         <v>1216</v>
       </c>
-      <c r="O242" s="24" t="s">
+      <c r="P242" s="24" t="s">
         <v>1217</v>
-      </c>
-      <c r="P242" s="24" t="s">
-        <v>1218</v>
       </c>
       <c r="Q242" s="24"/>
       <c r="R242" s="24" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="243" spans="2:18">
@@ -23203,7 +23200,7 @@
       <c r="D243" s="57"/>
       <c r="E243" s="57"/>
       <c r="F243" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G243" s="57" t="s">
         <v>523</v>
@@ -23212,20 +23209,20 @@
       <c r="I243" s="57"/>
       <c r="J243" s="57"/>
       <c r="K243" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="L243" s="57"/>
       <c r="M243" s="57"/>
       <c r="N243" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="O243" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="P243" s="57"/>
       <c r="Q243" s="57"/>
       <c r="R243" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="244" spans="2:18" ht="39.75">
@@ -23235,16 +23232,16 @@
         <v>234</v>
       </c>
       <c r="E244" s="56" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F244" s="56" t="s">
         <v>206</v>
       </c>
       <c r="G244" s="56" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H244" s="56" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I244" s="56"/>
       <c r="J244" s="56" t="s">
@@ -23258,13 +23255,13 @@
       </c>
       <c r="M244" s="56"/>
       <c r="N244" s="56" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="O244" s="56" t="s">
         <v>206</v>
       </c>
       <c r="P244" s="56" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="Q244" s="56"/>
       <c r="R244" s="56" t="s">
@@ -23327,71 +23324,71 @@
       <c r="B246" s="22"/>
       <c r="C246" s="6"/>
       <c r="D246" s="24" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E246" s="24" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F246" s="24" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G246" s="24" t="s">
         <v>1220</v>
       </c>
-      <c r="F246" s="24" t="s">
-        <v>1583</v>
-      </c>
-      <c r="G246" s="24" t="s">
-        <v>1221</v>
-      </c>
       <c r="H246" s="24" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="I246" s="24"/>
       <c r="J246" s="24" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K246" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="L246" s="24" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="M246" s="24"/>
       <c r="N246" s="24" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="O246" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="P246" s="24" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="Q246" s="24"/>
       <c r="R246" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="247" spans="2:18">
       <c r="B247" s="12"/>
       <c r="C247" s="34"/>
       <c r="D247" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E247" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F247" s="57"/>
       <c r="G247" s="57"/>
       <c r="H247" s="57"/>
       <c r="I247" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J247" s="57"/>
       <c r="K247" s="57"/>
       <c r="L247" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="M247" s="57"/>
       <c r="N247" s="57"/>
       <c r="O247" s="57"/>
       <c r="P247" s="57"/>
       <c r="Q247" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="R247" s="57"/>
     </row>
@@ -23399,20 +23396,20 @@
       <c r="B248" s="17"/>
       <c r="C248" s="6"/>
       <c r="D248" s="56" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E248" s="56" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F248" s="56" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G248" s="56"/>
       <c r="H248" s="56" t="s">
         <v>194</v>
       </c>
       <c r="I248" s="56" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="J248" s="56" t="s">
         <v>222</v>
@@ -23421,7 +23418,7 @@
         <v>204</v>
       </c>
       <c r="L248" s="56" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="M248" s="56"/>
       <c r="N248" s="56" t="s">
@@ -23434,7 +23431,7 @@
         <v>282</v>
       </c>
       <c r="Q248" s="56" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="R248" s="56"/>
     </row>
@@ -23494,42 +23491,42 @@
       <c r="B250" s="22"/>
       <c r="C250" s="6"/>
       <c r="D250" s="24" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E250" s="24" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="F250" s="24" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="G250" s="24"/>
       <c r="H250" s="24" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="I250" s="24" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="J250" s="24" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="K250" s="24" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="L250" s="24" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="M250" s="24"/>
       <c r="N250" s="24" t="s">
+        <v>1223</v>
+      </c>
+      <c r="O250" s="24" t="s">
         <v>1224</v>
       </c>
-      <c r="O250" s="24" t="s">
-        <v>1225</v>
-      </c>
       <c r="P250" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="Q250" s="24" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="R250" s="24"/>
     </row>
@@ -23538,14 +23535,14 @@
       <c r="C251" s="34"/>
       <c r="D251" s="57"/>
       <c r="E251" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F251" s="57"/>
       <c r="G251" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H251" s="57" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I251" s="57"/>
       <c r="J251" s="57"/>
@@ -23562,17 +23559,17 @@
       <c r="B252" s="17"/>
       <c r="C252" s="6"/>
       <c r="D252" s="56" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E252" s="56" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="F252" s="56"/>
       <c r="G252" s="56" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H252" s="56" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="I252" s="56"/>
       <c r="J252" s="56"/>
@@ -23627,17 +23624,17 @@
       <c r="B254" s="22"/>
       <c r="C254" s="6"/>
       <c r="D254" s="24" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E254" s="24" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="F254" s="24"/>
       <c r="G254" s="24" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H254" s="24" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="I254" s="24"/>
       <c r="J254" s="24"/>
@@ -23740,25 +23737,25 @@
       <c r="E259" s="14"/>
       <c r="F259" s="14"/>
       <c r="G259" s="14" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H259" s="14" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I259" s="14"/>
       <c r="J259" s="14"/>
       <c r="K259" s="14"/>
       <c r="L259" s="14" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="M259" s="14"/>
       <c r="N259" s="14" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="O259" s="14"/>
       <c r="P259" s="14"/>
       <c r="Q259" s="14" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="R259" s="14"/>
     </row>
@@ -23769,7 +23766,7 @@
         <v>272</v>
       </c>
       <c r="E260" s="18" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F260" s="18"/>
       <c r="G260" s="18" t="s">
@@ -23779,29 +23776,29 @@
         <v>244</v>
       </c>
       <c r="I260" s="18" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="J260" s="18" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K260" s="18"/>
       <c r="L260" s="18" t="s">
         <v>217</v>
       </c>
       <c r="M260" s="18" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="N260" s="18" t="s">
         <v>239</v>
       </c>
       <c r="O260" s="18" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="P260" s="18" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="Q260" s="18" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="R260" s="18"/>
     </row>
@@ -23861,42 +23858,42 @@
       <c r="B262" s="22"/>
       <c r="C262" s="6"/>
       <c r="D262" s="24" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E262" s="24" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F262" s="24"/>
       <c r="G262" s="24" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H262" s="24" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="I262" s="24" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J262" s="24" t="s">
         <v>1005</v>
-      </c>
-      <c r="J262" s="24" t="s">
-        <v>1006</v>
       </c>
       <c r="K262" s="24"/>
       <c r="L262" s="24" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="M262" s="24" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="N262" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O262" s="24" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="P262" s="24" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="Q262" s="24" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="R262" s="24"/>
     </row>
@@ -23906,14 +23903,14 @@
       <c r="D263" s="14"/>
       <c r="E263" s="14"/>
       <c r="F263" s="14" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="14"/>
       <c r="J263" s="14"/>
       <c r="K263" s="14" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L263" s="14"/>
       <c r="M263" s="14"/>
@@ -23930,42 +23927,42 @@
         <v>346</v>
       </c>
       <c r="E264" s="18" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F264" s="18" t="s">
         <v>239</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H264" s="18" t="s">
         <v>745</v>
       </c>
       <c r="I264" s="18" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J264" s="18"/>
       <c r="K264" s="18" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L264" s="18" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="M264" s="18" t="s">
         <v>263</v>
       </c>
       <c r="N264" s="18" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O264" s="18" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="P264" s="18" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="Q264" s="18"/>
       <c r="R264" s="18" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="265" spans="2:18" ht="58.5">
@@ -24024,56 +24021,56 @@
       <c r="B266" s="22"/>
       <c r="C266" s="6"/>
       <c r="D266" s="24" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E266" s="24" t="s">
         <v>1010</v>
       </c>
-      <c r="E266" s="24" t="s">
-        <v>1011</v>
-      </c>
       <c r="F266" s="24" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="G266" s="24" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H266" s="24" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="I266" s="24" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="J266" s="24"/>
       <c r="K266" s="24" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="L266" s="24" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="M266" s="24" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="N266" s="24" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="O266" s="24" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="P266" s="24" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="Q266" s="24"/>
       <c r="R266" s="24" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="267" spans="2:18">
       <c r="B267" s="12"/>
       <c r="C267" s="34"/>
       <c r="D267" s="14" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E267" s="14"/>
       <c r="F267" s="14" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
@@ -24095,10 +24092,10 @@
         <v>261</v>
       </c>
       <c r="E268" s="18" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F268" s="18" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G268" s="18" t="s">
         <v>266</v>
@@ -24153,16 +24150,16 @@
       <c r="B270" s="22"/>
       <c r="C270" s="6"/>
       <c r="D270" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E270" s="24" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="F270" s="24" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G270" s="24" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H270" s="24"/>
       <c r="I270" s="24"/>

--- a/output7/【河洛文讀注音-閩拼調符】《寒窯賦》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調符】《寒窯賦》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92303063-0E49-4E6D-97E9-8180F3EBD16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAD76692-1784-4437-A761-DF25CDDE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3873" uniqueCount="1647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3874" uniqueCount="1648">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -5677,12 +5677,15 @@
     <t>Han5-Iau7-Hu2.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>白話字</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44">
+  <fonts count="45">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5989,6 +5992,14 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FF000000"/>
+      <name val="台灣楷體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -6099,7 +6110,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6282,6 +6293,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8019,7 +8033,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>959</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -14478,7 +14492,7 @@
       <c r="Q3" s="54"/>
       <c r="R3" s="54"/>
       <c r="T3" s="16"/>
-      <c r="V3" s="61" t="s">
+      <c r="V3" s="62" t="s">
         <v>956</v>
       </c>
     </row>
@@ -14506,7 +14520,7 @@
       <c r="Q4" s="18"/>
       <c r="R4" s="18"/>
       <c r="S4" s="19"/>
-      <c r="V4" s="62"/>
+      <c r="V4" s="63"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="20">
@@ -14542,7 +14556,7 @@
       <c r="Q5" s="41"/>
       <c r="R5" s="41"/>
       <c r="S5" s="21"/>
-      <c r="V5" s="62"/>
+      <c r="V5" s="63"/>
     </row>
     <row r="6" spans="1:22" s="26" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="22"/>
@@ -14569,7 +14583,7 @@
       <c r="Q6" s="24"/>
       <c r="R6" s="24"/>
       <c r="S6" s="25"/>
-      <c r="V6" s="62"/>
+      <c r="V6" s="63"/>
     </row>
     <row r="7" spans="1:22" s="30" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="27"/>
@@ -14590,7 +14604,7 @@
       <c r="Q7" s="54"/>
       <c r="R7" s="54"/>
       <c r="S7" s="29"/>
-      <c r="V7" s="62"/>
+      <c r="V7" s="63"/>
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="17"/>
@@ -14610,7 +14624,7 @@
       <c r="Q8" s="18"/>
       <c r="R8" s="18"/>
       <c r="S8" s="19"/>
-      <c r="V8" s="62"/>
+      <c r="V8" s="63"/>
     </row>
     <row r="9" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="20">
@@ -14638,7 +14652,7 @@
       <c r="R9" s="41"/>
       <c r="S9" s="21"/>
       <c r="T9" s="16"/>
-      <c r="V9" s="62"/>
+      <c r="V9" s="63"/>
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="22"/>
@@ -14658,7 +14672,7 @@
       <c r="Q10" s="24"/>
       <c r="R10" s="24"/>
       <c r="S10" s="31"/>
-      <c r="V10" s="62"/>
+      <c r="V10" s="63"/>
     </row>
     <row r="11" spans="1:22" s="29" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="32"/>
@@ -14684,7 +14698,7 @@
       <c r="R11" s="54" t="s">
         <v>286</v>
       </c>
-      <c r="V11" s="62"/>
+      <c r="V11" s="63"/>
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
@@ -14730,7 +14744,7 @@
         <v>286</v>
       </c>
       <c r="S12" s="19"/>
-      <c r="V12" s="62"/>
+      <c r="V12" s="63"/>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="20">
@@ -14783,7 +14797,7 @@
         <v>776</v>
       </c>
       <c r="S13" s="21"/>
-      <c r="V13" s="62"/>
+      <c r="V13" s="63"/>
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
@@ -14829,7 +14843,7 @@
         <v>1178</v>
       </c>
       <c r="S14" s="31"/>
-      <c r="V14" s="62"/>
+      <c r="V14" s="63"/>
     </row>
     <row r="15" spans="1:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="12"/>
@@ -14861,7 +14875,7 @@
       <c r="P15" s="54"/>
       <c r="Q15" s="54"/>
       <c r="R15" s="54"/>
-      <c r="V15" s="62"/>
+      <c r="V15" s="63"/>
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="17"/>
@@ -14905,7 +14919,7 @@
         <v>194</v>
       </c>
       <c r="S16" s="19"/>
-      <c r="V16" s="62"/>
+      <c r="V16" s="63"/>
     </row>
     <row r="17" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="20">
@@ -14958,7 +14972,7 @@
         <v>787</v>
       </c>
       <c r="S17" s="21"/>
-      <c r="V17" s="62"/>
+      <c r="V17" s="63"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
@@ -15002,7 +15016,7 @@
         <v>985</v>
       </c>
       <c r="S18" s="31"/>
-      <c r="V18" s="62"/>
+      <c r="V18" s="63"/>
     </row>
     <row r="19" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="12"/>
@@ -15034,7 +15048,7 @@
         <v>1561</v>
       </c>
       <c r="R19" s="54"/>
-      <c r="V19" s="62"/>
+      <c r="V19" s="63"/>
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="17"/>
@@ -15080,7 +15094,7 @@
         <v>204</v>
       </c>
       <c r="S20" s="19"/>
-      <c r="V20" s="62"/>
+      <c r="V20" s="63"/>
     </row>
     <row r="21" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="20">
@@ -15133,7 +15147,7 @@
         <v>796</v>
       </c>
       <c r="S21" s="21"/>
-      <c r="V21" s="62"/>
+      <c r="V21" s="63"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
@@ -15179,7 +15193,7 @@
         <v>994</v>
       </c>
       <c r="S22" s="31"/>
-      <c r="V22" s="62"/>
+      <c r="V22" s="63"/>
     </row>
     <row r="23" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="12"/>
@@ -15205,7 +15219,7 @@
       </c>
       <c r="Q23" s="54"/>
       <c r="R23" s="54"/>
-      <c r="V23" s="62"/>
+      <c r="V23" s="63"/>
     </row>
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="17"/>
@@ -15251,7 +15265,7 @@
         <v>745</v>
       </c>
       <c r="S24" s="19"/>
-      <c r="V24" s="62"/>
+      <c r="V24" s="63"/>
     </row>
     <row r="25" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B25" s="20">
@@ -15304,7 +15318,7 @@
         <v>293</v>
       </c>
       <c r="S25" s="21"/>
-      <c r="V25" s="62"/>
+      <c r="V25" s="63"/>
     </row>
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="22"/>
@@ -15350,7 +15364,7 @@
         <v>995</v>
       </c>
       <c r="S26" s="31"/>
-      <c r="V26" s="62"/>
+      <c r="V26" s="63"/>
     </row>
     <row r="27" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="12"/>
@@ -15374,7 +15388,7 @@
         <f t="shared" ref="U27:U32" si="1" xml:space="preserve"> MID($N$26,4,1)</f>
         <v>i</v>
       </c>
-      <c r="V27" s="62"/>
+      <c r="V27" s="63"/>
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="17"/>
@@ -15400,7 +15414,7 @@
         <f t="shared" si="1"/>
         <v>i</v>
       </c>
-      <c r="V28" s="62"/>
+      <c r="V28" s="63"/>
     </row>
     <row r="29" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B29" s="20">
@@ -15435,7 +15449,7 @@
         <f t="shared" si="1"/>
         <v>i</v>
       </c>
-      <c r="V29" s="62"/>
+      <c r="V29" s="63"/>
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="22"/>
@@ -15461,7 +15475,7 @@
         <f t="shared" si="1"/>
         <v>i</v>
       </c>
-      <c r="V30" s="62"/>
+      <c r="V30" s="63"/>
     </row>
     <row r="31" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B31" s="12"/>
@@ -15485,7 +15499,7 @@
         <f t="shared" si="1"/>
         <v>i</v>
       </c>
-      <c r="V31" s="62"/>
+      <c r="V31" s="63"/>
     </row>
     <row r="32" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="17"/>
@@ -15509,7 +15523,7 @@
         <f t="shared" si="1"/>
         <v>i</v>
       </c>
-      <c r="V32" s="62"/>
+      <c r="V32" s="63"/>
     </row>
     <row r="33" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B33" s="20">
@@ -15536,7 +15550,7 @@
       <c r="Q33" s="41"/>
       <c r="R33" s="41"/>
       <c r="S33" s="21"/>
-      <c r="V33" s="62"/>
+      <c r="V33" s="63"/>
     </row>
     <row r="34" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="22"/>
@@ -15556,7 +15570,7 @@
       <c r="Q34" s="24"/>
       <c r="R34" s="24"/>
       <c r="S34" s="31"/>
-      <c r="V34" s="62"/>
+      <c r="V34" s="63"/>
     </row>
     <row r="35" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B35" s="12"/>
@@ -15588,7 +15602,7 @@
       <c r="R35" s="54" t="s">
         <v>343</v>
       </c>
-      <c r="V35" s="62"/>
+      <c r="V35" s="63"/>
     </row>
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="17"/>
@@ -15632,7 +15646,7 @@
         <v>346</v>
       </c>
       <c r="S36" s="19"/>
-      <c r="V36" s="62"/>
+      <c r="V36" s="63"/>
     </row>
     <row r="37" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B37" s="20">
@@ -15685,7 +15699,7 @@
         <v>306</v>
       </c>
       <c r="S37" s="21"/>
-      <c r="V37" s="62"/>
+      <c r="V37" s="63"/>
     </row>
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="22"/>
@@ -15729,7 +15743,7 @@
         <v>1009</v>
       </c>
       <c r="S38" s="31"/>
-      <c r="V38" s="62"/>
+      <c r="V38" s="63"/>
     </row>
     <row r="39" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B39" s="12"/>
@@ -15761,7 +15775,7 @@
       <c r="R39" s="54" t="s">
         <v>613</v>
       </c>
-      <c r="V39" s="62"/>
+      <c r="V39" s="63"/>
     </row>
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="17"/>
@@ -15807,7 +15821,7 @@
         <v>937</v>
       </c>
       <c r="S40" s="19"/>
-      <c r="V40" s="62"/>
+      <c r="V40" s="63"/>
     </row>
     <row r="41" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B41" s="20">
@@ -15860,7 +15874,7 @@
         <v>408</v>
       </c>
       <c r="S41" s="21"/>
-      <c r="V41" s="62"/>
+      <c r="V41" s="63"/>
     </row>
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="22"/>
@@ -15906,7 +15920,7 @@
         <v>1015</v>
       </c>
       <c r="S42" s="31"/>
-      <c r="V42" s="62"/>
+      <c r="V42" s="63"/>
     </row>
     <row r="43" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B43" s="12"/>
@@ -15934,7 +15948,7 @@
       <c r="P43" s="54"/>
       <c r="Q43" s="54"/>
       <c r="R43" s="54"/>
-      <c r="V43" s="62"/>
+      <c r="V43" s="63"/>
     </row>
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="17"/>
@@ -15976,7 +15990,7 @@
       <c r="Q44" s="56"/>
       <c r="R44" s="56"/>
       <c r="S44" s="19"/>
-      <c r="V44" s="62"/>
+      <c r="V44" s="63"/>
     </row>
     <row r="45" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B45" s="20">
@@ -16031,7 +16045,7 @@
 </v>
       </c>
       <c r="S45" s="21"/>
-      <c r="V45" s="62"/>
+      <c r="V45" s="63"/>
     </row>
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="22"/>
@@ -16073,7 +16087,7 @@
       <c r="Q46" s="24"/>
       <c r="R46" s="24"/>
       <c r="S46" s="31"/>
-      <c r="V46" s="62"/>
+      <c r="V46" s="63"/>
     </row>
     <row r="47" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B47" s="12"/>
@@ -16093,7 +16107,7 @@
       <c r="P47" s="54"/>
       <c r="Q47" s="54"/>
       <c r="R47" s="54"/>
-      <c r="V47" s="62"/>
+      <c r="V47" s="63"/>
     </row>
     <row r="48" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="17"/>
@@ -16113,7 +16127,7 @@
       <c r="Q48" s="18"/>
       <c r="R48" s="18"/>
       <c r="S48" s="19"/>
-      <c r="V48" s="62"/>
+      <c r="V48" s="63"/>
     </row>
     <row r="49" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B49" s="20">
@@ -16140,7 +16154,7 @@
       <c r="Q49" s="41"/>
       <c r="R49" s="41"/>
       <c r="S49" s="21"/>
-      <c r="V49" s="62"/>
+      <c r="V49" s="63"/>
     </row>
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="22"/>
@@ -16160,7 +16174,7 @@
       <c r="Q50" s="24"/>
       <c r="R50" s="24"/>
       <c r="S50" s="31"/>
-      <c r="V50" s="62"/>
+      <c r="V50" s="63"/>
     </row>
     <row r="51" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B51" s="12"/>
@@ -16182,7 +16196,7 @@
       <c r="P51" s="54"/>
       <c r="Q51" s="54"/>
       <c r="R51" s="54"/>
-      <c r="V51" s="62"/>
+      <c r="V51" s="63"/>
     </row>
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="17"/>
@@ -16228,7 +16242,7 @@
         <v>36</v>
       </c>
       <c r="S52" s="19"/>
-      <c r="V52" s="62"/>
+      <c r="V52" s="63"/>
     </row>
     <row r="53" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B53" s="20">
@@ -16281,7 +16295,7 @@
         <v>50</v>
       </c>
       <c r="S53" s="21"/>
-      <c r="V53" s="62"/>
+      <c r="V53" s="63"/>
     </row>
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="22"/>
@@ -16327,7 +16341,7 @@
         <v>1038</v>
       </c>
       <c r="S54" s="31"/>
-      <c r="V54" s="62"/>
+      <c r="V54" s="63"/>
     </row>
     <row r="55" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B55" s="12"/>
@@ -16353,7 +16367,7 @@
       <c r="R55" s="54" t="s">
         <v>326</v>
       </c>
-      <c r="V55" s="62"/>
+      <c r="V55" s="63"/>
     </row>
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="17"/>
@@ -16397,7 +16411,7 @@
         <v>939</v>
       </c>
       <c r="S56" s="19"/>
-      <c r="V56" s="62"/>
+      <c r="V56" s="63"/>
     </row>
     <row r="57" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B57" s="20">
@@ -16450,7 +16464,7 @@
         <v>540</v>
       </c>
       <c r="S57" s="21"/>
-      <c r="V57" s="62"/>
+      <c r="V57" s="63"/>
     </row>
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="22"/>
@@ -16494,7 +16508,7 @@
         <v>1051</v>
       </c>
       <c r="S58" s="31"/>
-      <c r="V58" s="62"/>
+      <c r="V58" s="63"/>
     </row>
     <row r="59" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B59" s="12"/>
@@ -16524,7 +16538,7 @@
       <c r="R59" s="54" t="s">
         <v>374</v>
       </c>
-      <c r="V59" s="62"/>
+      <c r="V59" s="63"/>
     </row>
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="17"/>
@@ -16570,7 +16584,7 @@
         <v>940</v>
       </c>
       <c r="S60" s="19"/>
-      <c r="V60" s="62"/>
+      <c r="V60" s="63"/>
     </row>
     <row r="61" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B61" s="20">
@@ -16623,7 +16637,7 @@
         <v>372</v>
       </c>
       <c r="S61" s="21"/>
-      <c r="V61" s="62"/>
+      <c r="V61" s="63"/>
     </row>
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="22"/>
@@ -16669,7 +16683,7 @@
         <v>1060</v>
       </c>
       <c r="S62" s="31"/>
-      <c r="V62" s="62"/>
+      <c r="V62" s="63"/>
     </row>
     <row r="63" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B63" s="12"/>
@@ -16691,7 +16705,7 @@
       <c r="P63" s="54"/>
       <c r="Q63" s="54"/>
       <c r="R63" s="54"/>
-      <c r="V63" s="62"/>
+      <c r="V63" s="63"/>
     </row>
     <row r="64" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="17"/>
@@ -16715,7 +16729,7 @@
       <c r="Q64" s="18"/>
       <c r="R64" s="18"/>
       <c r="S64" s="19"/>
-      <c r="V64" s="62"/>
+      <c r="V64" s="63"/>
     </row>
     <row r="65" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B65" s="20">
@@ -16748,7 +16762,7 @@
       <c r="Q65" s="41"/>
       <c r="R65" s="41"/>
       <c r="S65" s="21"/>
-      <c r="V65" s="62"/>
+      <c r="V65" s="63"/>
     </row>
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="22"/>
@@ -16772,7 +16786,7 @@
       <c r="Q66" s="24"/>
       <c r="R66" s="24"/>
       <c r="S66" s="31"/>
-      <c r="V66" s="62"/>
+      <c r="V66" s="63"/>
     </row>
     <row r="67" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B67" s="12"/>
@@ -16792,7 +16806,7 @@
       <c r="P67" s="54"/>
       <c r="Q67" s="54"/>
       <c r="R67" s="54"/>
-      <c r="V67" s="62"/>
+      <c r="V67" s="63"/>
     </row>
     <row r="68" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="17"/>
@@ -16812,7 +16826,7 @@
       <c r="Q68" s="18"/>
       <c r="R68" s="18"/>
       <c r="S68" s="19"/>
-      <c r="V68" s="62"/>
+      <c r="V68" s="63"/>
     </row>
     <row r="69" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B69" s="20">
@@ -16839,7 +16853,7 @@
       <c r="Q69" s="41"/>
       <c r="R69" s="41"/>
       <c r="S69" s="21"/>
-      <c r="V69" s="62"/>
+      <c r="V69" s="63"/>
     </row>
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="22"/>
@@ -16859,7 +16873,7 @@
       <c r="Q70" s="24"/>
       <c r="R70" s="24"/>
       <c r="S70" s="31"/>
-      <c r="V70" s="62"/>
+      <c r="V70" s="63"/>
     </row>
     <row r="71" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B71" s="12"/>
@@ -16889,7 +16903,7 @@
       <c r="R71" s="54" t="s">
         <v>389</v>
       </c>
-      <c r="V71" s="62"/>
+      <c r="V71" s="63"/>
     </row>
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="17"/>
@@ -16935,7 +16949,7 @@
         <v>941</v>
       </c>
       <c r="S72" s="19"/>
-      <c r="V72" s="62"/>
+      <c r="V72" s="63"/>
     </row>
     <row r="73" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B73" s="20">
@@ -16988,7 +17002,7 @@
         <v>395</v>
       </c>
       <c r="S73" s="21"/>
-      <c r="V73" s="62"/>
+      <c r="V73" s="63"/>
     </row>
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="22"/>
@@ -17034,7 +17048,7 @@
         <v>1068</v>
       </c>
       <c r="S74" s="31"/>
-      <c r="V74" s="62"/>
+      <c r="V74" s="63"/>
     </row>
     <row r="75" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B75" s="12"/>
@@ -17066,7 +17080,7 @@
         <v>1561</v>
       </c>
       <c r="R75" s="54"/>
-      <c r="V75" s="62"/>
+      <c r="V75" s="63"/>
     </row>
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="17"/>
@@ -17112,7 +17126,7 @@
         <v>1048</v>
       </c>
       <c r="S76" s="19"/>
-      <c r="V76" s="62"/>
+      <c r="V76" s="63"/>
     </row>
     <row r="77" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B77" s="20">
@@ -17165,7 +17179,7 @@
         <v>31</v>
       </c>
       <c r="S77" s="21"/>
-      <c r="V77" s="62"/>
+      <c r="V77" s="63"/>
     </row>
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="22"/>
@@ -17211,7 +17225,7 @@
         <v>1049</v>
       </c>
       <c r="S78" s="31"/>
-      <c r="V78" s="62"/>
+      <c r="V78" s="63"/>
     </row>
     <row r="79" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B79" s="12"/>
@@ -17237,7 +17251,7 @@
       <c r="P79" s="54"/>
       <c r="Q79" s="54"/>
       <c r="R79" s="54"/>
-      <c r="V79" s="62"/>
+      <c r="V79" s="63"/>
     </row>
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="17"/>
@@ -17277,7 +17291,7 @@
       <c r="Q80" s="18"/>
       <c r="R80" s="18"/>
       <c r="S80" s="19"/>
-      <c r="V80" s="62"/>
+      <c r="V80" s="63"/>
     </row>
     <row r="81" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B81" s="20">
@@ -17328,7 +17342,7 @@
       <c r="Q81" s="41"/>
       <c r="R81" s="41"/>
       <c r="S81" s="21"/>
-      <c r="V81" s="62"/>
+      <c r="V81" s="63"/>
     </row>
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="22"/>
@@ -17368,7 +17382,7 @@
       <c r="Q82" s="24"/>
       <c r="R82" s="24"/>
       <c r="S82" s="31"/>
-      <c r="V82" s="63"/>
+      <c r="V82" s="64"/>
     </row>
     <row r="83" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B83" s="12"/>
@@ -24211,13 +24225,15 @@
       <c r="Q272" s="18"/>
       <c r="R272" s="18"/>
     </row>
-    <row r="273" spans="2:18" ht="58.5">
+    <row r="273" spans="2:18" ht="62.25">
       <c r="B273" s="20">
         <f>B269+1</f>
         <v>68</v>
       </c>
       <c r="C273" s="6"/>
-      <c r="D273" s="41"/>
+      <c r="D273" s="61" t="s">
+        <v>95</v>
+      </c>
       <c r="E273" s="41"/>
       <c r="F273" s="41"/>
       <c r="G273" s="42"/>

--- a/output7/【河洛文讀注音-閩拼調符】《寒窯賦》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調符】《寒窯賦》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAD76692-1784-4437-A761-DF25CDDE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F60BDA49-EB65-4F50-912F-16A22C8652D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView minimized="1" xWindow="31920" yWindow="3045" windowWidth="28800" windowHeight="11295" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>

--- a/output7/【河洛文讀注音-閩拼調符】《寒窯賦》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調符】《寒窯賦》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F60BDA49-EB65-4F50-912F-16A22C8652D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EB029C3-D23A-48D0-81F0-5D2F323B2E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="31920" yWindow="3045" windowWidth="28800" windowHeight="11295" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="31920" yWindow="3045" windowWidth="28800" windowHeight="11295" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
